--- a/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A318"/>
+  <dimension ref="A1:A490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/index.php/en/109483/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
@@ -466,2191 +466,3395 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
+          <t>https://www.aninews.in/news/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/amp_articleshow/123993745.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167786</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday</t>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
+          <t>https://www.ptinews.com/detail/national/Local-bodies-in-MP-s-Raisen-passed-resolutions-supporting-One-Nation-One-Election-Chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.uniindia.com/photoes/638785.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://www.ptinews.com/detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pm-s-blessings-chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.ptinews.com/editor-detail/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mp-s-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
+          <t>https://english.newsnationtv.com/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-J-K/2930370</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638786.html</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638671.html</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638785.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra-7115311.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638668.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638670.html</t>
+          <t>https://indiapublickhabar.com/Agriculture/shivraj-singh-agricultural-growth-food-basket-india-2025/4795</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638071.html</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638735.html</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638794.html</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AF%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95%E0%A5%87-%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2-%E0%A4%95%E0%A4%AE-%E0%A4%A8/ar-AA1tKoCZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A5%88%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%AA%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%9C%E0%A5%81%E0%A4%9F-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1LuZyz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://neindiabroadcast.com/2025/09/20/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://www.msn.com/hi-in/news/other/kartikeya-wedding-photo-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%AF-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7%E0%A5%82%E0%A4%AE-%E0%A4%A5-%E0%A4%B0%E0%A4%95%E0%A4%A4-%E0%A4%A8%E0%A4%9C%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%A6-%E0%A4%A8-%E0%A4%82-%E0%A4%AC%E0%A4%B9%E0%A5%82/ar-AA1Aq18G?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A4%B2-%E0%A4%97%E0%A4%88-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A4-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%A6-%E0%A4%B7-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%B8%E0%A4%96%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88/ar-AA1KGssn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%9C%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A5%87%E0%A4%98%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%B2-%E0%A4%97-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87%E0%A4%AE%E0%A4%B2%E0%A4%AA-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%97-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%82%E0%A4%B8%E0%A5%82-%E0%A4%AA-%E0%A4%82%E0%A4%9B%E0%A4%95%E0%A4%B0-9-%E0%A4%B2-%E0%A4%96-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A6-%E0%A4%A6/ar-AA1DBLvQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%82-%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE-%E0%A4%B0-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AB%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%AC-%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%82%E0%A4%A6%E0%A4%97-%E0%A4%B9-%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4%E0%A4%AC-%E0%A4%B9/ar-AA1MT4zW</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-chauhan-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A6-%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%A6-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B2%E0%A4%97%E0%A4%A4-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82/ar-AA1G4kSw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html?utm_source=article_detail&amp;utm_medium=CRE&amp;utm_campaign=latestnews_CRE</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9A-%E0%A4%A8%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%A4%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97%E0%A4%88%E0%A4%82-%E0%A4%B5-%E0%A4%AF%E0%A4%B0%E0%A4%B2/ar-AA1xALne?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%9F-%E0%A4%B0%E0%A4%97%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%AE-%E0%A4%B9%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A6%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%B8-%E0%A4%B9%E0%A4%A4/ar-AA1MqaDa?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A4%B2-%E0%A4%B2-%E0%A4%B9%E0%A5%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%A7-%E0%A4%96%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%A4-%E0%A4%86%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%9C%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%B8-%E0%A4%A7/ar-AA1xUk9d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/raisen-mp-fake-fertilizer-conflicting-statements-shivraj-singh-chouhan-aidal-singh-kansana-shock-farmers-9650353.html</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%AD%E0%A4%B0-%E0%A4%B8-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1u1cBq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%A4-%E0%A4%B8-%E0%A4%8F-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AF-%E0%A4%A6%E0%A4%97-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MHFyB</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE-%E0%A4%A8%E0%A4%B9-%E0%A4%A8-%E0%A4%AE-%E0%A4%AE%E0%A4%B2-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%B0-%E0%A4%B9%E0%A4%A4-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%97%E0%A4%A4-%E0%A4%AA%E0%A5%87%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%9C-%E0%A4%B0-%E0%A4%B0%E0%A4%96/ar-AA1BdzrP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.msn.com/hi-in/news/other/mgnrega-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A4-%E0%A4%94%E0%A4%B0-%E0%A4%9C%E0%A4%B5-%E0%A4%AC%E0%A4%A6%E0%A5%87%E0%A4%B9-%E0%A4%95-%E0%A4%B8%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1uZF53?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF%E0%A5%82%E0%A4%B0-%E0%A4%AF-%E0%A4%86%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1Mqmi4?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%AE%E0%A4%AA-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B0%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B8%E0%A5%81%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%86%E0%A4%9C-%E0%A4%9C-%E0%A4%B0-%E0%A4%B9-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%B5-%E0%A4%B0%E0%A4%82%E0%A4%9F/ar-AA1qUS4m?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://rashtriyahindimail.in/posts/111331</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AE%E0%A5%8D%E0%A4%B8%E0%A4%9F%E0%A5%87%E0%A4%95-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%95%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A5%81%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1Cwv9k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-by-election-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A8-%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%A4-%E0%A4%B0/ar-AA1syDww?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%9C-%E0%A4%A4-%E0%A4%87%E0%A4%9C%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AD-%E0%A4%97-%E0%A4%B2-%E0%A4%AF/ar-AA1Eqc4V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/madhya-pradesh/shivraj-singh-chouhan-on-a-visit-to-raisen-districphp/cid17449225.htm</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A5%87%E0%A4%A6%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-cm-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%95-%E0%A4%9A-%E0%A4%9F%E0%A5%8D%E0%A4%A0/ar-AA1wPCa5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%B2-%E0%A4%AC-%E0%A4%9C-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%97%E0%A4%8F-%E0%A4%AA-%E0%A4%9B%E0%A5%87/ar-AA1sCHcC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/india-israel-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%B0-%E0%A4%87%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AA%E0%A5%82%E0%A4%B8-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B8-%E0%A4%B0%E0%A4%B9/ar-AA1CvKsJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%86%E0%A4%82%E0%A4%A6-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82/ar-AA1vC8f0?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%86%E0%A4%B2-%E0%A4%9A%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1DqpoB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/21/moral-responsibility-of-every-citizen-to-keep-his.html</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rural-development-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%AD%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1wUMo8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A4%A8-%E0%A4%A5-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%9F%E0%A4%B6%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%87%E0%A4%B8-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A6-%E0%A4%97%E0%A5%8D%E0%A4%97%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%8F%E0%A4%82%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%9F/ar-AA1z4w81?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/gst-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%82-%E0%A4%B2-%E0%A4%AD/ar-AA1MSiQO?ocid=finance-verthp-feeds</t>
+          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%94%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-msp-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1zzqhC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%82%E0%A4%A7%E0%A5%81-%E0%A4%9C%E0%A4%B2-%E0%A4%B8%E0%A4%82%E0%A4%A7-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A4%A0%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1F0ALw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/shivraj-singh-chouhan-participated-in-a-cleanliness-drive-in-raisen-as-part-of-the-seva-pakhwada-4277570</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/big-1/government-leave-no-stone-unturned-helping-farmers-shivraj-chauhan-told-flood-victims/</t>
+          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/pm-modi-birthday-shivraj-singh-chouhan-launches-healthy-women-strong-family-campaign-plants-75-saplings-in-pus</t>
+          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/110-road-works-approved-udhampur-jitendra-singh-expresses-gratitude-shivraj-singh/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop--4276499</t>
+          <t>https://thenewsmill.com/2025/09/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/jammu-and-kashmir-shivraj-singh-chouhan-met-flood-affected-farmers</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
+          <t>https://divyakirti.com/archives/5675</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/shivraj-singh-chouhan-noticed-a-cow-sitting-on-the-road-and-said-i-will-come-again-in-the-evening/</t>
+          <t>https://www.bhaskar.com/mp-oth-mat-latest-neemuch-news-024503-2124969-nor.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mp-news-union-agriculture-minister-shivraj-singh-chouhan-called-the-collector-in-sehore-and-directed-him-to-immediately-survey-the-damaged-crops/</t>
+          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%B8%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95/</t>
+          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.outlookhindi.com/country/general/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-102444</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://mediapassion.co.in/?p=67079</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%AE-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%9C%E0%A4%AE-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%9C-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-pm-kisan-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1N2dx0?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
+          <t>http://www.msn.com/hi-in/news/other/karnataka-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%A8-%E0%A4%9F%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%AA-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1MXeLi?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/shivraj-recalls-meeting-pm-modi-on-his-birthday-4270868</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/?amp=1</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/even-after-years-pm-modi-remains-connected-with-the-workers/115314/amp/</t>
+          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-18-september-national-international-sports-2756435.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://azadsipahi.in/09/2025/shivraj-chauhan-gave-birthday-wish-to-prime-minister-modi-the-story-of-the-first-meeting.html</t>
+          <t>https://www.msn.com/en-in/news/India/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-shivraj-singh-chouhan/ar-AA1MAvVi</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://azadsipahi.in/09/2025/agriculture-minister-shivraj-chauhan-will-meet-tomorrow-for-gst-reforms-on-agricultural-machinery.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership?amp</t>
+          <t>https://www.aninews.in/news/national/general-news/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation20250922140426</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
+          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/pm-kisan-20th-installment-%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%9D-%E0%A4%B2-%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%A8%E0%A4%A6-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87%E0%A4%97-20500-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%8F/ar-AA1JA7Hp</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.bignewsnetwork.com/news/278582056/defence-minister-rajnath-singh-shares-my-modi-story-on-pm-75th-birthday-praises-his-discipline-profound-knowledge</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
+          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.jammulinksnews.com/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-j-k-10479980</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://m-hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.msn.com/hi-in/news/other/agriculture-%E0%A4%A6%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%A4-%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%A6-%E0%A4%B5-%E0%A4%B0-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%B0-%E0%A4%A1%E0%A4%AE%E0%A5%88%E0%A4%AA/ar-AA1MEFla?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-6-%E0%A4%AC%E0%A4%9C%E0%A5%87-6-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%96%E0%A4%AC%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A5%8D-%E0%A4%B5-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%9A%E0%A5%82%E0%A4%B9-%E0%A4%82-%E0%A4%95-%E0%A4%86%E0%A4%82%E0%A4%A4%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%8F-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87/ar-AA1M0HhF?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/breaking-news-in-hindi/liveblog/58166012.cms</t>
+          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/haryana/chandigarh-city-rahul-gandhi-habit-of-making-false-allegations-then-running-away-haryana-cm-nayab-singh-saini-on-vote-chori-9647747.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/current-affairs/todays-current-affairs-in-hindi-for-21-september-2025</t>
+          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
+          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218/amp</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/delhi/shivraj-singh-chauhan-told-the-story-of-first-meeting-with-modi-ji</t>
+          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%BE-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://deshbandhump.com/%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE-%E0%A4%AA%E0%A4%96%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A4%BC%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.khabarwala24.com/national/seva-pakhwada-bjp-ruled-states-to-organize-various-programs-on-prime-minister-modis/101297/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html/amp</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html/amp</t>
+          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/raisen-mein-shivraj-singh-ne-ek-rashtr-ek-chunav-ke-liye-janpratinidhiyon-ko-dilai-shapath/103967/</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630162-strategizing-himalayan-agriculture-calls-for-specialized-policies-and-education</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/centre-to-procure-green-gram--black-gram--sunflower-from-karnataka--union-minister-pralhad-joshi/2933070</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/amp/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-emphasises-crop-diversification-for-a-sustainable-agricultural-system-enn25091803601</t>
+          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://thekashmirhorizon.com/2025/09/20/union-agri-minister-chauhan-pledges-full-support-to-jk-farmers/</t>
+          <t>https://www.devdiscourse.com/article/politics/3628306-rahul-gandhi-visits-flood-hit-areas-in-amritsar-gurdaspur</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
+          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654/</t>
+          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638734.html</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Bhagwant-Mann-assures-to-raise-arhtiyas-demands-with-Centre/2931607</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.msn.com/en-in/news/India/nath-began-bulldozer-action-after-honey-trap-case-shivraj-mohan-too-went-for-it-in-bhopal/ar-AA1u1IuG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jda-cracks-down-on-unauthorised-construction-at-domana-nardani/</t>
+          <t>https://hindi.oneindia.com/videos/fertilizer-and-seed-shortage-in-vidisha-shivraj-singh-chouhan-cm-mohan-yadav-4264565.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.thekashmirmonitor.net/pm-stands-by-people-of-jk-chouhan/</t>
+          <t>https://www.ibc24.in/madhya-pradesh/peoples-representatives-of-raisen-district-passed-resolution-in-support-of-one-nation-one-election-shivraj-singh-chouhan-3262147.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MOmec?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision?amp</t>
+          <t>https://hindi.etnownews.com/personal-finance/pm-kisan-21st-installment-without-land-documents-border-areas-farmers-can-still-benefit-from-pm-kisan-yojana-check-details-heree-article-152876946</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities?amp</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448?amp=1</t>
+          <t>https://www.amarujala.com/haryana/hisar/chief-minister-naib-singh-saini-said-adopt-diversification-in-agriculture-give-priority-to-coarse-cereals-hisar-news-c-21-hsr1020-715039-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister-1/amp/</t>
+          <t>https://www.kisantak.in/politics/story/haryana-farmer-schemes-agriculture-diversification-nayab-singh-saini-prv-1280721-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/amp/business/farmers-to-gain-as-agri-minister-pushes-gst-cut-benefit-for-tractors-equipment-articleshow-lipd50k</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/?amp</t>
+          <t>https://eng.ruralvoice.in/opinion/talks-on-us-tariffs-begin-again-will-tariffs-upend-indian-agriculture.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/index.php</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/?amp=1</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html/amp</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0%E0%A4%AC-%E0%A4%95-%E0%A4%A8%E0%A5%8D%E0%A4%AB%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B8-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-250-%E0%A4%B2-%E0%A4%96-%E0%A4%AE-%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%AC-%E0%A4%9C-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A4%96-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF/ar-AA1MEprL</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/?noamp=mobile&amp;amp</t>
+          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+          <t>https://www.msn.com/en-in/politics/government/brics-nations-launch-land-restoration-partnership-to-stop-desertification-and-soil-fertility-loss/ar-AA1Dbt7Q?ocid=BingNewsSerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://patnapress.com/bihar-self-employment-schemes-entrepreneurs/amp/?noamp=mobile</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://statetimes.in/amp/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%B8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%B8/ar-AA1tsiMG?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/procurement-%E0%A4%AE%E0%A5%82%E0%A4%82%E0%A4%97%E0%A4%AB%E0%A4%B2-%E0%A4%94%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%AC-%E0%A4%A8-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%85%E0%A4%B5%E0%A4%A7-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%95-%E0%A4%B9-%E0%A4%97-100-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%96%E0%A4%B0-%E0%A4%A6/ar-AA1yKSox?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.prameyanews.com/news-post/nation/two-day-national-agriculture-conference-begins-to-strategise-for-rabi-season-2025</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/bhadohi/gyanpur/news/women-empowerment-campaign-in-bhadohi-135934797.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.amarujala.com/delhi-ncr/noida/positive-news-in-district-na-news-c-121-1-pbt1011-144312-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://mediapassion.co.in/?p=66795</t>
+          <t>https://www.amarujala.com/haryana/sonipat/gift-of-gymnasiums-indoor-gyms-and-womens-cultural-centre-sonipat-news-c-197-1-snp1001-142698-2025-09-23</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/sultanpur/news/bike-rally-under-mission-shakti-in-sultanpur-135977475.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/gauriganj/story-mission-shakti-phase-5-launched-in-amethi-focus-on-women-s-safety-and-empowerment-201758384351430.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/pusa-fourth-convocation-bihar-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%94%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%95-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9/ar-AA1IMIBJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/agra/saiyan/news/mission-shakti-live-broadcast-of-chief-minister-from-lucknow-135969992.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/khategaon-mahila-bal-vikas-supervisor-amita-jat-and-project-officer-pranay-maheshwar-dispute-19950165</t>
+          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B2-%E0%A4%B2-%E0%A4%AE-%E0%A4%A3-%E0%A4%A8%E0%A5%87-vc-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97-%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%87%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A4%B9-56-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-fir-%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%AE-%E0%A4%A8-%E0%A4%9F%E0%A4%B0-%E0%A4%82%E0%A4%97-%E0%A4%94%E0%A4%B0/ar-AA1KyF3w?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/krishi-mela-rabi-2025-to-be-held-in-hisar-on-september-21-22/?amp=1</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/kendriya-mantri-shivraj-ne-kisanon-ke-soybean-ki-fasal-kharab-hone-ki-shikayat-par-adhikari-ko-survey-ka-diya-nirdesh/103594/</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://mpbreakingnews.in/chhattisgarh/annapurna-devi-met-cm-vishnudev-sai-discussed-women-empowerment-and-child-development-52-819875</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/bijnor-farmer-electrocuted-in-field-villagers-block-highway-with-body-1280227-2025-09-20</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/paddy-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B2-%E0%A4%A8%E0%A5%8D%E0%A4%9A-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE-%E0%A4%8F%E0%A4%A1-%E0%A4%9F%E0%A5%87%E0%A4%A1-%E0%A4%A7-%E0%A4%A8-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97-30-%E0%A4%A4%E0%A4%95-%E0%A4%87%E0%A4%9C-%E0%A4%AB-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1E8rJq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/economy-and-business/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
+          <t>https://lalluram.com/punjab-government-women-empowerment-scheme-1100-rupees-monthly-allowance/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/</t>
+          <t>https://www.dotookmedia.com/2025/09/50_20.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/chandigarh-haryana/haryana-is-making-a-big-contribution-in-food-security-shyam-singh-rana-chandigarh-haryana-news-c-16-1-pkl1095-820762-2025-09-17</t>
+          <t>https://jantaserishta.com/delhi-ncr/delhi-cm-stresses-on-womens-health-and-empowerment-at-aiims-4279950</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://sbharatnews.com/?p=139033</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://janaagaj.in/teachers-should-develop-the-habit-of-reading-books-in-children-governor/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A4%BC-%E0%A4%98-%E0%A4%9F-%E0%A4%B2-700-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A5%82%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-150-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-158-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2-%E0%A4%B8%E0%A4%AC%E0%A5%8D%E0%A4%B8-%E0%A4%A1/ar-AA1MCt9k</t>
+          <t>https://federalbharat.com/national-resolution-of-healthy-women-strong-family-witness-gadkari-shared-the-historic-moment-of-noida/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://cg24news.in/cm-20949</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/22/Uttarakhand-UKSSSC-Exam-Viral.html</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://newsheight.com/big-breaking-healthy-women-social-family/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/money/topstories/gst-reforms-to-inject-rs-2-lakh-cr-into-economy-boost-demand-across-sectors/ar-AA1MPDtb?ocid=finance-verthp-feeds</t>
+          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/latest-news/story/punjab-cm-bhagwant-mann-announces-price-cuts-for-verka-s-milk-and-cooperative-products-swm-1280239-2025-09-20</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-ministrys-special-campaign-5-0-will-start-from-october-2-work-will-be-done-on-e-waste-and-complaints/</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/north-india-heavy-rainfall-update-himachal-uttarakhand-cloudburst-landslide-dehradun-deaths-delhi-up-bihar-maharashtra-weather-alert-2025/</t>
+          <t>https://devbhoomimedia.com/cm-dhami-in-kashipur-sammelan/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/business/indian-agriculture-will-achieve-top-global-growth-of-37-in-q1-2025-26-4269188</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%AF-%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-75-%E0%A4%9C-%E0%A4%B2-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8/ar-AA1MJ8ti</t>
+          <t>https://bharat24live.com/news/bihar-nitish-government-will-transfer-5000-to-the-accounts-of-50-lakh-women-today</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+          <t>https://bolchhattisgarh.in/chief-minister-sai-laid-the-foundation-stone-and-inaugurated-77-development-works-of-development-works-worth-rs-245-crore-80-lakh/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://samacharsamrat.com/agriculture-ministry-to-inform-farmers-about-the-benefits-of-gst-rate-revision/</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
+          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://annews.co.in/15476/</t>
+          <t>https://www.hindektatimes.com/204154/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://webvarta.com/states/other-state/sonipat-lado-lakshmi-yojana-mega-camp-2025/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://webvarta.com/states/other-state/haryana-cm-nayab-saini-sonipat-projects/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
+          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
+          <t>https://rajkajlive.com/chief-minister-dhami-inaugurated-the-exhibition-in-the-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/auspicious-time-to-buy-a-tractor-from-navratri-to-diwali/?amp=1</t>
+          <t>https://www.saahassamachar.in/fifth-phase-of-mission-shakti-to-commence-from-sharad-navratri-chief-minister</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/top-3-john-deere-tractor-models-in-india-price-and-features/?amp=1</t>
+          <t>https://upstox.com/news/business-news/latest-updates/india-us-trade-talks-back-on-track-amid-tariff-tensions-positive-forward-looking/article-181419/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://upstox.com/news/business-news/latest-updates/mother-dairy-to-pass-100-gst-benefit-cuts-prices-on-milk-paneer-butter-ghee-and-safal-foods/article-181384/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/CM-Dr-Yadav-congratulated-PM-Modi-on-his-birthday.php</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/main-objective-of-skill-development-schemes-is-to.php</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/chief-minister-nitish-kumar-expanded-the-chief-ministers-determination-self-help-allowance-scheme-in-bihar/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-stands-with-jk-flood-victims-agriculture-minister-4275258</t>
+          <t>https://thebharatnow.in/others-state/centres-relief-plan-punjab-floods-declared-extreme-disaster-farmers-to-get-compensation-state-to-get-loan/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/videos/national/CVBNCVBCVB</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=questions-about-the-functioning-of-municipal-corporations-cm-yogi-orders-review-of-mayors-powers-which-may-be-curtailed-576957</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/bollywoods-go-to-travel-destinations-youll-want-to-visit/london/slideshow/123943268.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://www.sakshipost.com/news/india-remains-heart-growth-journey-tech-firm-nothing-raises-200-million-452836</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/satna-maihar-daylight-robbery-8-lakh-lclk-strc-2333321-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>https://awaaz24x7.com/news/haryana-a-program-was-organized-in-panchkula-to-commemorate-maharaja-agrasen-jayanti-chief-minister-nayab-singh-saini-attended-and-extended-greetings-for-the-sharadiya-navratri</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/rahul-gandhi-visits-flood-affected-areas-in-amritsar-and-gurdaspur-meets-victims/869119/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/delhi-ncr/when-did-the-opposition-talk-about-reforms-gajendra-singh-shekhawat-4279867</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/chh-rai-hmu-mat-latest-raipur-news-050504-1407740-nor.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/-75--1188144</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1186696</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>https://sanjeevanisamachar.com/story-of-former-bihar-chief-minister-daroga-prasad-rai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>https://swatvasamachar.com/news/nawada-news-2224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1187827</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>https://www.rajyasameeksha.com/politics</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/telangana/the-chief-justice-of-the-high-court-urged-the-chief-minister-to-enhance-facilities-in-the-courts-4277697</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/dewas-news-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%A8%E0%A5%8D-%E0%A4%A8-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%A8%E0%A4%97%E0%A5%8D%E0%A4%A8-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%81%E0%A4%9F%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%B2-%E0%A4%B8%E0%A5%9C%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%9A%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%95%E0%A5%8D-%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9C%E0%A4%B0/ar-AA1It9zG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Rain-havoc-continues-in-Dehradun-one-student-died.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Security-forces-recovered-looted-weapons-in-Manipu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Aim-to-make-India-a-leader-in-biofuel-and-green-tr.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>https://e-webcareit.com/cooperation-in-cooperation-programme-organised-at-raj-bhavan-two-important-agreements-signed-in-the-presence-of-governor-and-chief-minister</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Engineers-Research-and-Training-Institute-will-be.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/stock-re-categorization/slideshow/123940116.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/india/cm-pushkar-singh-dhami-expressed-gratitude-to-the-cag-report-on-the-achievement-of-revenue-surplus-3493975.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>https://firstbihar.com/bihar/patna-news/advocates-will-get-5000-rs-per-month-stipend-in-bihar-nitish-kumar-government-announced-879143</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278588801/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>https://postmanindia.in/chief-minister-inaugurated-the-swachh-utsav-programme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>https://rajpanchhi.com/posts/68d0f60ba09cd6cfc1b3f89e-H1QpM_-Ek-tree-%E2%80%94-mother-s-name-campaign-Chief-Minister-Bhajanlal-Sharma-gave-a-message-of-environmental-protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>https://shouryagatha.com/main-stories/himalayan-environmental-dialogue-program-speakers-took-various-measures-for-environmental-balance-in-the-desamvivi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>https://bolpanipat.com/cleanliness-is-the-only-way-to-have-a-healthy-and-prosperous-life-ceo-dr-kiran-singh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>https://knewsindia.in/big-breaking-2/major-relief-for-festivals-in-delhi-rekha-gupta-government-allows-loudspeakers-to-be-played-till-12-midnight/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/chief-minister-wishes-the-people-of-the-state-on-himalaya-day-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>https://apnuuttarakhand.com/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90140</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90048</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90190</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://sehorehulchal.com/news/farmers-devastated-by-double-attack-cm-helpline-flooded-with-complaints/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-yogi-adityanath-said-up-working-towards-viksit-uttar-pradesh-vision2047-24055474.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/raipur-news/cm-claims-gst-2-0-provides-relief-to-all-sections-tractors-19964857</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/video/madhya-pradesh/rewa/the-chief-minister-gave-a-gift-of-rs16231-crore-to-tyonthar-rewa-news-c-1-1-noi1337-3425344-2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-providing-the-best-fertilizers-seeds-and-pesticides-to-farmers-is-our-priority-dr-kirori-lal-news-hindi-1-753391-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>https://best24news.com/haryana/haryana-news-haryana-cm-saini-gave-a-big/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%97-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A4-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%97-%E0%A4%B0-%E0%A4%B5%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1MTb2R?ocid=finance-verthp-feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/gst-cuts-from-22nd-september-ensure-benefits-reach-farmers-says-agriculture-minister-shivraj-singh-chouhan-ddb79</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/17-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-approves-110-road-projects-worth-rs-2000-crore-for-udhampur-4278710</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>https://makdaiexpress24.com/devotees-climbed-1063-stairs-to-seek-the-blessings-of-maihars-mother-sharda-and-pooja-mais-blessings-in-brahmamuhurta/</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A490"/>
+  <dimension ref="A1:A412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
@@ -466,35 +466,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
@@ -522,28 +522,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
@@ -564,77 +564,77 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
+          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Local-bodies-in-MP-s-Raisen-passed-resolutions-supporting-One-Nation-One-Election-Chouhan/2936291</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
@@ -648,126 +648,126 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pm-s-blessings-chouhan/2929985</t>
+          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.uniindia.com/shivraj-assesses-damages-of-crops-in-jammu-announces-relief-measures-for-farmers-disaster-victims/north/news/3583526.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.uniindia.com/photoes/638787.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra-7115311.html</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Agriculture/shivraj-singh-agricultural-growth-food-basket-india-2025/4795</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
@@ -802,21 +802,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AF%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95%E0%A5%87-%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2-%E0%A4%95%E0%A4%AE-%E0%A4%A8/ar-AA1tKoCZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
@@ -830,3031 +830,2485 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A5%88%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%AA%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%9C%E0%A5%81%E0%A4%9F-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1LuZyz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/kartikeya-wedding-photo-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%AF-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7%E0%A5%82%E0%A4%AE-%E0%A4%A5-%E0%A4%B0%E0%A4%95%E0%A4%A4-%E0%A4%A8%E0%A4%9C%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%A6-%E0%A4%A8-%E0%A4%82-%E0%A4%AC%E0%A4%B9%E0%A5%82/ar-AA1Aq18G?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A4%B2-%E0%A4%97%E0%A4%88-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A4-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%A6-%E0%A4%B7-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%B8%E0%A4%96%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88/ar-AA1KGssn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%9C%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A5%87%E0%A4%98%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%B2-%E0%A4%97-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87%E0%A4%AE%E0%A4%B2%E0%A4%AA-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%97-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%82%E0%A4%B8%E0%A5%82-%E0%A4%AA-%E0%A4%82%E0%A4%9B%E0%A4%95%E0%A4%B0-9-%E0%A4%B2-%E0%A4%96-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A6-%E0%A4%A6/ar-AA1DBLvQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%82-%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE-%E0%A4%B0-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AB%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%AC-%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%82%E0%A4%A6%E0%A4%97-%E0%A4%B9-%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4%E0%A4%AC-%E0%A4%B9/ar-AA1MT4zW</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
+          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A4%B2-%E0%A4%B2-%E0%A4%B9%E0%A5%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%A7-%E0%A4%96%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%A4-%E0%A4%86%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%9C%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%B8-%E0%A4%A7/ar-AA1xUk9d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%A4-%E0%A4%B8-%E0%A4%8F-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AF-%E0%A4%A6%E0%A4%97-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MHFyB</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mgnrega-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A4-%E0%A4%94%E0%A4%B0-%E0%A4%9C%E0%A4%B5-%E0%A4%AC%E0%A4%A6%E0%A5%87%E0%A4%B9-%E0%A4%95-%E0%A4%B8%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1uZF53?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111331</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AE%E0%A5%8D%E0%A4%B8%E0%A4%9F%E0%A5%87%E0%A4%95-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%95%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A5%81%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1Cwv9k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-by-election-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A8-%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%A4-%E0%A4%B0/ar-AA1syDww?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
+          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
+          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.patrika.com/bhopal-news/notification-issued-to-change-the-name-of-alirajpur-district-to-aalirajpur-19947549</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative/</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://divyakirti.com/archives/5675</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
+          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/mp-oth-mat-latest-neemuch-news-024503-2124969-nor.html</t>
+          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%AE-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%9C%E0%A4%AE-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%9C-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-pm-kisan-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1N2dx0?ocid=finance-verthp-feeds</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/karnataka-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%A8-%E0%A4%9F%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%AA-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1MXeLi?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://patnapress.com/bihar-assembly-horse-trading-scandal-bjp-mla-questioned/amp/?noamp=mobile</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-18-september-national-international-sports-2756435.html</t>
+          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-shivraj-singh-chouhan/ar-AA1MAvVi</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Arrest-of-Mehraj-Malik-is-illegal.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation20250922140426</t>
+          <t>https://www.patrika.com/bhopal-news/mp-got-golden-banyan-award-honoured-by-union-minister-gajendra-singh-shekhawat-at-heritage-tourism-best-state-category-19945617</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rain-alert-in-8-districts-imd-issues-warning-19964265</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rainfall-in-next-12-hours-alert-issued-in-3-districts-warns-imd-19953418</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.patrika.com/bhopal-news/2-big-mines-of-mp-will-yield-gold-after-singrauli-this-district-is-preparing-gold-mine-in-mp-19951211</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://mradubhashi.com/news.php?id=forest-minister-kedar-kashyap-paid-tribute-to-bharat-ratna-visvesvaraya-576675</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278582056/defence-minister-rajnath-singh-shares-my-modi-story-on-pm-75th-birthday-praises-his-discipline-profound-knowledge</t>
+          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://patnapress.com/eci-mandates-ai-election-content-labels/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://patnapress.com/foreign-pilgrims-russia-ukraine-gaya-ancestral-rites/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
+          <t>https://patnapress.com/solar-eclipse-live-stream-2025/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://patnapress.com/pawan-singh-bihar-2025-elections-reality-show-exit/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://patnapress.com/solar-eclipse-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://patnapress.com/navratri-2025-goddess-shailputri-traditional-offerings/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://patnapress.com/nitish-kumar-construction-workers-aid/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://patnapress.com/patna-ipsowa-tree-festival-bihta/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/agriculture-%E0%A4%A6%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%A4-%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%A6-%E0%A4%B5-%E0%A4%B0-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%B0-%E0%A4%A1%E0%A4%AE%E0%A5%88%E0%A4%AA/ar-AA1MEFla?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://patnapress.com/pawan-kumar-bhimappa-bajantri-sworn-in-patna-high-court-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://www.newstak.in/bihar/story/chirag-paswan-bihar-nda-seat-sharing-statement-3203457-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
+          <t>https://insiderlive.in/bihar-election-2025-congress-candidate-selection-seat-sharing/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%BE-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80/</t>
+          <t>https://insiderlive.in/bihar-goreyakothi-vidhansabha-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE-%E0%A4%AA%E0%A4%96%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A4%BC%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://insiderlive.in/bihar-baniapur-vidhan-sabha-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/seva-pakhwada-bjp-ruled-states-to-organize-various-programs-on-prime-minister-modis/101297/</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
+          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
+          <t>https://theindianawaaz.com/gst-cut-on-farm-equipment-must-benefit-farmers-directly-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628306-rahul-gandhi-visits-flood-hit-areas-in-amritsar-gurdaspur</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nath-began-bulldozer-action-after-honey-trap-case-shivraj-mohan-too-went-for-it-in-bhopal/ar-AA1u1IuG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/fertilizer-and-seed-shortage-in-vidisha-shivraj-singh-chouhan-cm-mohan-yadav-4264565.html</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/madhya-pradesh/peoples-representatives-of-raisen-district-passed-resolution-in-support-of-one-nation-one-election-shivraj-singh-chouhan-3262147.html</t>
+          <t>https://www.kadwaghut.com/?p=260993</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MOmec?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://hindi.etnownews.com/personal-finance/pm-kisan-21st-installment-without-land-documents-border-areas-farmers-can-still-benefit-from-pm-kisan-yojana-check-details-heree-article-152876946</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://www.ptinews.com/editor-detail/kerala-governor--cm-wish-pm-modi-on-his-75th-birthday/2921961</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/hisar/chief-minister-naib-singh-saini-said-adopt-diversification-in-agriculture-give-priority-to-coarse-cereals-hisar-news-c-21-hsr1020-715039-2025-09-22</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/haryana-farmer-schemes-agriculture-diversification-nayab-singh-saini-prv-1280721-2025-09-21</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/opinion/talks-on-us-tariffs-begin-again-will-tariffs-upend-indian-agriculture.html</t>
+          <t>https://www.kadwaghut.com/?p=260445</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
+          <t>https://www.global-agriculture.com/india-region/prime-minister-modi-lays-foundation-stone-of-indias-first-pm-mitra-park-in-madhya-pradesh/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://thecsrjournal.in/bihar-mukhyamantri-mahila-rojgar-yojana-hindi/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
+          <t>https://www.jagran.com/bihar/patna-city-bihar-govt-jobs-women-entrepreneurship-nitish-kumar-employement-drive-24050839.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/politics/government/brics-nations-launch-land-restoration-partnership-to-stop-desertification-and-soil-fertility-loss/ar-AA1Dbt7Q?ocid=BingNewsSerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://patnapress.com/bihar-self-employment-schemes-entrepreneurs/amp/?noamp=mobile</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%B8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%B8/ar-AA1tsiMG?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://livevns.news/Top-Headlines/cm-yogi-launches-mission-shakti-50-special-program-in/cid17447412.htm</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
+          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/bhadohi/gyanpur/news/women-empowerment-campaign-in-bhadohi-135934797.html</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/delhi-ncr/noida/positive-news-in-district-na-news-c-121-1-pbt1011-144312-2025-09-21</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/sonipat/gift-of-gymnasiums-indoor-gyms-and-womens-cultural-centre-sonipat-news-c-197-1-snp1001-142698-2025-09-23</t>
+          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/sultanpur/news/bike-rally-under-mission-shakti-in-sultanpur-135977475.html</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/gauriganj/story-mission-shakti-phase-5-launched-in-amethi-focus-on-women-s-safety-and-empowerment-201758384351430.html</t>
+          <t>https://amanyatralive.com/%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C%E0%A4%BC-5-%E0%A4%95%E0%A4%BE-%E0%A4%B6%E0%A5%81%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/agra/saiyan/news/mission-shakti-live-broadcast-of-chief-minister-from-lucknow-135969992.html</t>
+          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
+          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.hindektatimes.com/204154/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
+          <t>https://aavaj.com/jaunpur/jaunpur-news-%E0%A4%9C%E0%A5%8C%E0%A4%A8%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C-5-0-%E0%A4%95/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://www.newstak.in/utility-news/story/pm-kisan-21st-installment-update-notification-2025-3202470-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/chhattisgarh/annapurna-devi-met-cm-vishnudev-sai-discussed-women-empowerment-and-child-development-52-819875</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://lalluram.com/punjab-government-women-empowerment-scheme-1100-rupees-monthly-allowance/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.dotookmedia.com/2025/09/50_20.html</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/delhi-cm-stresses-on-womens-health-and-empowerment-at-aiims-4279950</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://sbharatnews.com/?p=139033</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://janaagaj.in/teachers-should-develop-the-habit-of-reading-books-in-children-governor/</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://federalbharat.com/national-resolution-of-healthy-women-strong-family-witness-gadkari-shared-the-historic-moment-of-noida/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://cg24news.in/cm-20949</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-healthy-women-social-family/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://devbhoomimedia.com/cm-dhami-in-kashipur-sammelan/</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://bharat24live.com/news/bihar-nitish-government-will-transfer-5000-to-the-accounts-of-50-lakh-women-today</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://bolchhattisgarh.in/chief-minister-sai-laid-the-foundation-stone-and-inaugurated-77-development-works-of-development-works-worth-rs-245-crore-80-lakh/</t>
+          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.hindektatimes.com/204154/</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://webvarta.com/states/other-state/sonipat-lado-lakshmi-yojana-mega-camp-2025/</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://webvarta.com/states/other-state/haryana-cm-nayab-saini-sonipat-projects/</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://rajkajlive.com/chief-minister-dhami-inaugurated-the-exhibition-in-the-municipal-corporation/</t>
+          <t>https://vocaltv.in/madhya-pradesh/the-chief-minister-will-unveil-the-statue-of-a-conphp/cid17426496.htm</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.saahassamachar.in/fifth-phase-of-mission-shakti-to-commence-from-sharad-navratri-chief-minister</t>
+          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/business-news/latest-updates/india-us-trade-talks-back-on-track-amid-tariff-tensions-positive-forward-looking/article-181419/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/business-news/latest-updates/mother-dairy-to-pass-100-gst-benefit-cuts-prices-on-milk-paneer-butter-ghee-and-safal-foods/article-181384/</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/others-state/centres-relief-plan-punjab-floods-declared-extreme-disaster-farmers-to-get-compensation-state-to-get-loan/</t>
+          <t>https://insiderlive.in/rjd-family-dispute-rohini-acharya-controversy/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/bollywoods-go-to-travel-destinations-youll-want-to-visit/london/slideshow/123943268.cms</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://insiderlive.in/giriraj-singh-attack-opposition-bihar-politics/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/india-remains-heart-growth-journey-tech-firm-nothing-raises-200-million-452836</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/satna-maihar-daylight-robbery-8-lakh-lclk-strc-2333321-2025-09-15</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://awaaz24x7.com/news/haryana-a-program-was-organized-in-panchkula-to-commemorate-maharaja-agrasen-jayanti-chief-minister-nayab-singh-saini-attended-and-extended-greetings-for-the-sharadiya-navratri</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/rahul-gandhi-punjab-visit.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/rahul-gandhi-visits-flood-affected-areas-in-amritsar-and-gurdaspur-meets-victims/869119/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Armys-winter-storage-train-returns-with-753-tonnes.html</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/ED-notice-to-Yuvraj-Singh-Robin-Uthappa-Sonu-Sood.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/when-did-the-opposition-talk-about-reforms-gajendra-singh-shekhawat-4279867</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.jagmarg.com/sonipat/chief-minister-nayab-singh-saini-gave-a-big-gift-inaugurated-557-projects-worth-about-rs-117-crore</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/chh-rai-hmu-mat-latest-raipur-news-050504-1407740-nor.html</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://m.economictimes.com/markets/stocks/stock-liveblog/tech-mahindra-share-price-today-live-updates-16-sep-2025/liveblog/123911873.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://m.economictimes.com/markets/stocks/news/7-penny-stocks-surge-up-to-55-in-just-5-days-did-you-invest-in-any/kesoram-industries/slideshow/124024203.cms</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-75--1188144</t>
+          <t>https://m.economictimes.com/markets/stocks/news/redington-among-7-stocks-that-closed-above-vwap-on-sept-16/bullish-trend/slideshow/123934660.cms</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186696</t>
+          <t>https://m.economictimes.com/markets/stocks/news/garden-reach-shipbuilders-among-4-stocks-that-formed-bullish-white-marubozu-pattern/zen-technologies/slideshow/123962841.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/new-entrants/slideshow/123940009.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://m.economictimes.com/markets/stocks/news/15-mfs-add-these-10-stocks-in-august-25-4-stocks-rally-over-50-in-fy26/mankind-pharma/slideshow/123896518.cms</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://sanjeevanisamachar.com/story-of-former-bihar-chief-minister-daroga-prasad-rai/</t>
+          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://swatvasamachar.com/news/nawada-news-2224/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1187827</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-dhami-visited-the-disaster-affected-areas-and-directed-to-provide-immediate-financial-assistance-and-basic-services-to-all-affected-families-as-per-disaster-standards/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
+          <t>https://firstindia.co.in/news/madhya-pradesh/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.rajyasameeksha.com/politics</t>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/telangana/the-chief-justice-of-the-high-court-urged-the-chief-minister-to-enhance-facilities-in-the-courts-4277697</t>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1188553</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/dewas-news-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%A8%E0%A5%8D-%E0%A4%A8-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%A8%E0%A4%97%E0%A5%8D%E0%A4%A8-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%81%E0%A4%9F%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%B2-%E0%A4%B8%E0%A5%9C%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%9A%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%95%E0%A5%8D-%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9C%E0%A4%B0/ar-AA1It9zG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Rain-havoc-continues-in-Dehradun-one-student-died.html</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Security-forces-recovered-looted-weapons-in-Manipu.html</t>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+          <t>https://samvaad365.com/dehradun-cm-dhami-wishes-pm-modi-on-his-birthday-and-launches-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Aim-to-make-India-a-leader-in-biofuel-and-green-tr.html</t>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://e-webcareit.com/cooperation-in-cooperation-programme-organised-at-raj-bhavan-two-important-agreements-signed-in-the-presence-of-governor-and-chief-minister</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Engineers-Research-and-Training-Institute-will-be.php</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/stock-re-categorization/slideshow/123940116.cms</t>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/cm-pushkar-singh-dhami-expressed-gratitude-to-the-cag-report-on-the-achievement-of-revenue-surplus-3493975.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628939-haryana-cm-meets-union-minister-pralhad-joshi-to-discuss-farmer-welfare-and-procurement-issues?amp</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://firstbihar.com/bihar/patna-news/advocates-will-get-5000-rs-per-month-stipend-in-bihar-nitish-kumar-government-announced-879143</t>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278588801/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+          <t>https://makdaiexpress24.com/in-the-name-of-a-garden-mother-the-campaign-deputy-commissioner-mnrega-council-mr-singh-reviewed-the-works/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://postmanindia.in/chief-minister-inaugurated-the-swachh-utsav-programme/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>https://rajpanchhi.com/posts/68d0f60ba09cd6cfc1b3f89e-H1QpM_-Ek-tree-%E2%80%94-mother-s-name-campaign-Chief-Minister-Bhajanlal-Sharma-gave-a-message-of-environmental-protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>https://shouryagatha.com/main-stories/himalayan-environmental-dialogue-program-speakers-took-various-measures-for-environmental-balance-in-the-desamvivi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>https://bolpanipat.com/cleanliness-is-the-only-way-to-have-a-healthy-and-prosperous-life-ceo-dr-kiran-singh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>https://knewsindia.in/big-breaking-2/major-relief-for-festivals-in-delhi-rekha-gupta-government-allows-loudspeakers-to-be-played-till-12-midnight/</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/chief-minister-wishes-the-people-of-the-state-on-himalaya-day-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>https://apnuuttarakhand.com/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90140</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90048</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90190</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>https://sehorehulchal.com/news/farmers-devastated-by-double-attack-cm-helpline-flooded-with-complaints/</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-yogi-adityanath-said-up-working-towards-viksit-uttar-pradesh-vision2047-24055474.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/raipur-news/cm-claims-gst-2-0-provides-relief-to-all-sections-tractors-19964857</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/rewa/the-chief-minister-gave-a-gift-of-rs16231-crore-to-tyonthar-rewa-news-c-1-1-noi1337-3425344-2025-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-providing-the-best-fertilizers-seeds-and-pesticides-to-farmers-is-our-priority-dr-kirori-lal-news-hindi-1-753391-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>https://best24news.com/haryana/haryana-news-haryana-cm-saini-gave-a-big/</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%97-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A4-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%97-%E0%A4%B0-%E0%A4%B5%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1MTb2R?ocid=finance-verthp-feeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/gst-cuts-from-22nd-september-ensure-benefits-reach-farmers-says-agriculture-minister-shivraj-singh-chouhan-ddb79</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>https://www.drishtiias.com/statepcs/17-09-2025/bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-approves-110-road-projects-worth-rs-2000-crore-for-udhampur-4278710</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/devotees-climbed-1063-stairs-to-seek-the-blessings-of-maihars-mother-sharda-and-pooja-mais-blessings-in-brahmamuhurta/</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A412"/>
+  <dimension ref="A1:A500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
@@ -466,49 +466,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
@@ -522,21 +522,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
@@ -550,210 +550,210 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638785.html</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/shivraj-assesses-damages-of-crops-in-jammu-announces-relief-measures-for-farmers-disaster-victims/north/news/3583526.html</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638787.html</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
         </is>
       </c>
     </row>
@@ -767,133 +767,133 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111289</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
@@ -907,2406 +907,3022 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.bhaskarhindi.com/city/new-delhi/delhi-news-dalahan-aur-tilahan-ka-utpaadan-badhaane-ke-lie-rodamaip-banaakar-hoga-kaamah-shivaraaj-1187595</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://divyakirti.com/archives/5675</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/notification-issued-to-change-the-name-of-alirajpur-district-to-aalirajpur-19947549</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
+          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://statetimes.in/will-discuss-plying-of-all-vehicular-types-on-jmu-sgr-nh-with-gadkari-cm/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://statetimes.in/from-safe-houses-to-subterranean-sanctuaries-terror-outfits-change-tactics/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://statetimes.in/peace-prerequisite-for-tourism-sports-sectors-to-flourish-in-jk-cm/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://patnapress.com/bihar-assembly-horse-trading-scandal-bjp-mla-questioned/amp/?noamp=mobile</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://www.agniban.com/several-events-were-held-in-bjp-ruled-states-on-prime-minister-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Arrest-of-Mehraj-Malik-is-illegal.html</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-got-golden-banyan-award-honoured-by-union-minister-gajendra-singh-shekhawat-at-heritage-tourism-best-state-category-19945617</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rain-alert-in-8-districts-imd-issues-warning-19964265</t>
+          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/legislative-trojan-horse-mallikarjun-kharge-slams-bjp-over-bill-on-removal-of-pm-cm-ministers/articleshow/123893656.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rainfall-in-next-12-hours-alert-issued-in-3-districts-warns-imd-19953418</t>
+          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/2-big-mines-of-mp-will-yield-gold-after-singrauli-this-district-is-preparing-gold-mine-in-mp-19951211</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=forest-minister-kedar-kashyap-paid-tribute-to-bharat-ratna-visvesvaraya-576675</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://patnapress.com/eci-mandates-ai-election-content-labels/</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://patnapress.com/foreign-pilgrims-russia-ukraine-gaya-ancestral-rites/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://patnapress.com/solar-eclipse-live-stream-2025/</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://patnapress.com/pawan-singh-bihar-2025-elections-reality-show-exit/</t>
+          <t>https://www.ptinews.com/editor-detail/CPI-must-emerge-as-a-strong-force-that-can-shape-India-s-political-course-D-Raja/2936350</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://patnapress.com/solar-eclipse-september-2025/</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://patnapress.com/navratri-2025-goddess-shailputri-traditional-offerings/</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://patnapress.com/nitish-kumar-construction-workers-aid/</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://patnapress.com/patna-ipsowa-tree-festival-bihta/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://patnapress.com/pawan-kumar-bhimappa-bajantri-sworn-in-patna-high-court-chief-justice/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/chirag-paswan-bihar-nda-seat-sharing-statement-3203457-2025-09-22</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-election-2025-congress-candidate-selection-seat-sharing/</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-goreyakothi-vidhansabha-election-2025/</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-baniapur-vidhan-sabha-election-2025/</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://www.msn.com/hi-in/news/other/agri-rural-news-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7-%E0%A4%A8-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0%E0%A4%9C-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A5%8D%E0%A4%AF/ar-AA1MMI5R</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/gst-cut-on-farm-equipment-must-benefit-farmers-directly-agriculture-minister/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://upuklive.com/business/the-21st-installment-of-pm-farmer-will-come-soon-for-the-farmers-a-gift-of-rs-2000-will-come-soon-23960.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260993</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://statetimes.in/former-hurriyat-chief-abdul-gani-bhat-passes-away/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://statetimes.in/cme-cum-brainstorming-session-organised-by-mru-gmc-jammu/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/kerala-governor--cm-wish-pm-modi-on-his-75th-birthday/2921961</t>
+          <t>https://himachaldastak.com/chief-minister-tourism-start-up-scheme-gets-approval/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/himachal-government-will-bear-the-expenses-of-marriage-of-orphan-children-2216300</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-govt-makes-ekyc-mandatory-for-beneficiaries-of/cid17441579.htm</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://www.theindiadaily.com/state/punjab/cashless-treatment-up-to-rs-10-lakh-punjab-first-state-in-the-country-to-launch-the-chief-minister-s-health-scheme-news-94860</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260445</t>
+          <t>https://www.livehindustan.com/uttarakhand/rudrapur/story-uttarakhand-cm-pushkar-singh-dhami-visits-khatima-listens-to-public-concerns-201758294392599.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/prime-minister-modi-lays-foundation-stone-of-indias-first-pm-mitra-park-in-madhya-pradesh/</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/bihar-mukhyamantri-mahila-rojgar-yojana-hindi/</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/2-more-doctors-appointed-in-dhaneta-hospital-2213561</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/aligarh/story-aligarh-wholesalers-demand-action-against-fake-drug-dealers-at-cdf-up-annual-meeting-201758578893110.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://raigarhtopnews.com/chief-minister-vishnudev-sai-attended-2/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-ministers-instructions-ready-on-dm-ground-zero-in-disaster-affected-areas/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-bihar-govt-jobs-women-entrepreneurship-nitish-kumar-employement-drive-24050839.html</t>
+          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/himachal-education-reform-cbse-curriculum-rajiv-gandhi-schools-student-loan-scheme-54-818476</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/setback-for-congress-karnataka-hc-invalidates-malur-mlas-election-orders-recounting-of-votes/articleshow/123923092.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://newsarenaindia.com/nation/rajnath-shares-my-modi-story-praises-discipline-knowledge/56623</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/a-driver-was-bitten-by-a-snake-and-taken-to-the-hospital-but-was-released-as-soon-as-he-was-shown-to-a-doctor-in-ujjain/articleshow/123980598.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://livevns.news/Top-Headlines/cm-yogi-launches-mission-shakti-50-special-program-in/cid17447412.htm</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mahakal-mandir-pandit-pujari-appointments-controversy-indore-high-court-seeks-answers-ujjain-collector-in-3-months/articleshow/123947146.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/ujjain-railway-station-accident-army-truck-caught-fire-loaded-in-goods-train-railway-staff-control-no-casualty-reported/articleshow/124024940.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://insiderlive.in/ujiyarpur-vidhan-sabha-chunav-analysis/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://www.ptinews.com/editor-detail/RSS-leader-stresses-on-strengthening-Hindu-society-to-counter-global-conspiracies/2938144</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://amanyatralive.com/%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C%E0%A4%BC-5-%E0%A4%95%E0%A4%BE-%E0%A4%B6%E0%A5%81%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%82/</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.hindektatimes.com/204154/</t>
+          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
+          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://aavaj.com/jaunpur/jaunpur-news-%E0%A4%9C%E0%A5%8C%E0%A4%A8%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C-5-0-%E0%A4%95/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/utility-news/story/pm-kisan-21st-installment-update-notification-2025-3202470-2025-09-17</t>
+          <t>https://deshbandhump.com/congress-factionalism-came-out-in-the-open-in-front-of-the-leader-of-opposition/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-provided-financial-approval-of-rs-127-crore-for-various-development-schemes/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://citiupdate.com/news/detailNews/104931</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
+          <t>https://www.babushahi.com/business.php?id=210834</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/uae-firms-keen-to-invest-in-indian-infra-banking-startups-logistics-sectors-commerce-minister-piyush-goyal/articleshow/124001887.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/cm-nayab-singh-saini-mega-road-upgradation-project-647580</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/madhya-pradesh/the-chief-minister-will-unveil-the-statue-of-a-conphp/cid17426496.htm</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
+          <t>https://www.sabguru.com/haryana-cm-nayab-singh-saini-inaugurates-557-projects-worth-about-rs-117-crore-in-sonipat</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/delhi-cm-rekha-gupta-launches-song-for-pm-narendra-modis-birthday/articleshow/123921234.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
+          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/rjd-family-dispute-rohini-acharya-controversy/</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/giriraj-singh-attack-opposition-bihar-politics/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.dainiktribuneonline.com/news/rohtak/chief-minister-vishwakarma-samman-yojana-launched-artisans-will-get-a-top-up-incentive-of-rs-5000/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
+          <t>https://www.etvbharat.com/hi/!bharat/tamilnadu-chief-minister-stalin-launches-anbu-karangal-scheme-hindi-news-hin25091503706</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-viksit-bharat-viksit-uttar-pradesh-2047-workshop-in-gorakhpur-24049561.html</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/rahul-gandhi-punjab-visit.html</t>
+          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Armys-winter-storage-train-returns-with-753-tonnes.html</t>
+          <t>https://cnin.co.in/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%BE-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80-%E0%A4%AA%E0%A4%B0-%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%BF%E0%A4%95.../70476</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/ED-notice-to-Yuvraj-Singh-Robin-Uthappa-Sonu-Sood.html</t>
+          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+          <t>https://rghnews.com/cg-news-raipur-62/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+          <t>https://rghnews.com/cg-news-today-89/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.jagmarg.com/sonipat/chief-minister-nayab-singh-saini-gave-a-big-gift-inaugurated-557-projects-worth-about-rs-117-crore</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/stock-liveblog/tech-mahindra-share-price-today-live-updates-16-sep-2025/liveblog/123911873.cms</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/7-penny-stocks-surge-up-to-55-in-just-5-days-did-you-invest-in-any/kesoram-industries/slideshow/124024203.cms</t>
+          <t>https://smefutures.com/moil-starts-manganese-exports-as-state-trading-enterprise/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/redington-among-7-stocks-that-closed-above-vwap-on-sept-16/bullish-trend/slideshow/123934660.cms</t>
+          <t>https://indiaeducationdiary.in/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/garden-reach-shipbuilders-among-4-stocks-that-formed-bullish-white-marubozu-pattern/zen-technologies/slideshow/123962841.cms</t>
+          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/new-entrants/slideshow/123940009.cms</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/15-mfs-add-these-10-stocks-in-august-25-4-stocks-rally-over-50-in-fy26/mankind-pharma/slideshow/123896518.cms</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/maharashtra-urges-centre-to-double-onion-export-subsidy-to-support-farmers</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-dhami-visited-the-disaster-affected-areas-and-directed-to-provide-immediate-financial-assistance-and-basic-services-to-all-affected-families-as-per-disaster-standards/</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/madhya-pradesh/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+          <t>https://www.kisantak.in/news/trending/story/amit-shah-advises-farmers-to-reduce-use-of-pesticides-and-fertilizers-swm-1281204-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1188553</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+          <t>https://www.aajtak.in/uttar-pradesh/story/yogi-adityanath-writes-pm-narendra-modi-birthday-wishes-ntc-dskc-2335103-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://samvaad365.com/dehradun-cm-dhami-wishes-pm-modi-on-his-birthday-and-launches-swachh-utsav-2025/</t>
+          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628939-haryana-cm-meets-union-minister-pralhad-joshi-to-discuss-farmer-welfare-and-procurement-issues?amp</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/india-us-ties-tested-after-trump-attack-yet-still-stronger-than-chinas-trust-gap-says-us-foreign-policy-expert/articleshow/123939627.cms</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://smefutures.com/india-oman-trade-agreement-fta-oman-trade-deal/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/in-the-name-of-a-garden-mother-the-campaign-deputy-commissioner-mnrega-council-mr-singh-reviewed-the-works/</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/eu-eyes-deeper-india-partnership-despite-concerns-over-moscow-ties/articleshow/123943367.cms</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/indias-exports-likely-to-grow-6-per-cent-this-year-piyush-goyal/articleshow/123947681.cms</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/igf-qetci-sign-pact-to-develop-uk-india-quantum-value-chain-map/articleshow/123996773.cms</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/us-revokes-sanctions-exemption-on-irans-chabahar-port-what-it-means-for-indias-strategic-gateway/articleshow/123979793.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/india-in-advanced-talks-with-oman-for-fta-open-to-trade-deals-with-other-gcc-nations-piyush-goyal/articleshow/124001364.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/politics-and-nation/tripura-opposition-unhappy-with-no-business-in-assembly-on-sept-22-due-to-pm-modis-visit/articleshow/123999325.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/bihar/patna-pm-narendra-modi-purnia-rally-nitish-kumar-statement-on-lalan-singh-nda-politics-analysis-bihar-chunav-9628128.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>https://www.agniban.com/bihar-chief-minister-nitish-kumar-met-union-home-minister-amit-shah/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/tech/newsletters/morning-dispatch/the-h-1b-silver-lining-festive-sales-day-1-surge/articleshow/124059068.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/small-biz/sustainability/bizarre-climate-ideas-show-how-far-off-track-we-are/articleshow/123965955.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>https://awaaz24x7india.com/news/uttarakhand-events-were-held-across-the-state-on-prime-minister-modis-birthday-cm-dhami-inaugurated-the-swachh-utsav-2025-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>https://statetimes.in/dc-jammu-reviews-functioning-of-swd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>https://www.punjabnewsexpress.com/business/news/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-297667</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>https://cg24news.in/bjp-20925</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
         </is>

--- a/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A500"/>
+  <dimension ref="A1:A543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
@@ -459,84 +459,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
@@ -550,1869 +550,1869 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168649</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/new-delhi/delhi-news-dalahan-aur-tilahan-ka-utpaadan-badhaane-ke-lie-rodamaip-banaakar-hoga-kaamah-shivaraaj-1187595</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://www.etvbharat.com/hi/!state/after-vijayvargiya-meeting-with-home-minister-amit-shah-bjp-held-high-level-meeting-at-cm-house-madhya-pradesh-news-mps25092003187</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://divyakirti.com/archives/5675</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-17-18-september-live-updates-pm-narendra-modi-75th-birthday-bihar-election-bjp-amit-shah-rahul-gandhi-supreme-court/4145200/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://statetimes.in/will-discuss-plying-of-all-vehicular-types-on-jmu-sgr-nh-with-gadkari-cm/</t>
+          <t>https://indianlooknews.com/?p=56810</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://statetimes.in/from-safe-houses-to-subterranean-sanctuaries-terror-outfits-change-tactics/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://statetimes.in/peace-prerequisite-for-tourism-sports-sectors-to-flourish-in-jk-cm/</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://www.etvbharat.com/hi/!state/bjp-mla-rajeev-singh-parichha-and-mla-ravi-sharma-came-face-to-face-over-inspector-in-jhansi-uttar-pradesh-news-ups25091500787</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://www.etvbharat.com/hi/!state/sub-inspector-sunil-kumar-rai-slaps-bjp-worker-in-mirzapur-ssp-suspended-departmental-inquiry-started-uttar-pradesh-news-ups25092003608</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://firstindia.co.in/articles/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/several-events-were-held-in-bjp-ruled-states-on-prime-minister-modis-75th-birthday/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/legislative-trojan-horse-mallikarjun-kharge-slams-bjp-over-bill-on-removal-of-pm-cm-ministers/articleshow/123893656.cms</t>
+          <t>https://eng.ruralvoice.in/national/ghaziabad-farmer-neelam-tyagi-honoured-with-dr-norman-e-borlaug-innovative-farmer-award-2025.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/CPI-must-emerge-as-a-strong-force-that-can-shape-India-s-political-course-D-Raja/2936350</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://www.kisantak.in/knowledge/story/food-grain-production-expected-to-increase-by-24-percent-despite-floods-and-disasters-1278860-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://eng.ruralvoice.in/state/ap-govt-offers-rs-800-incentive-per-bag-to-farmers-who-cut-urea-use.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india-plans-rs-2-billion-fund-to-boost-infrastructure-finance/78815</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://statetimes.in/cbi-chargesheets-anil-ambani-rana-kapoor-in-rs-2796-crore-corruption-case/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://navbharattimes.indiatimes.com/state/punjab-and-haryana/chandigarh/registration-for-cashless-treatment-rs-10-lakh-under-chief-minister-health-scheme-will-start-from-september-23-bhagwant-mann-announces/articleshow/124050803.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://www.bhaskar.com/career/news/union-cabinet-approves-bio-ride-scheme-atishi-will-take-oath-as-chief-minister-on-september-21-133669316.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://argusenglish.in/national/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/agri-rural-news-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7-%E0%A4%A8-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0%E0%A4%9C-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A5%8D%E0%A4%AF/ar-AA1MMI5R</t>
+          <t>https://english.publictv.in/maharashtra-indian-railways-renames-ahmednagar-railway-station-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://www.bhaskar.com/local/bihar/darbhanga/news/darbhanga-cricket-associations-annual-general-meeting-was-held-new-district-committee-was-elected-135989912.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://upuklive.com/business/the-21st-installment-of-pm-farmer-will-come-soon-for-the-farmers-a-gift-of-rs-2000-will-come-soon-23960.html</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
+          <t>https://www.bhaskar.com/local/haryana/charkhi-dadri/news/charkhi-dadri-mla-sunil-satpal-sangwan-monsoon-session-assembly-dadri-rohtak-road-tender-construction-issue-public-works-department-minister-ranbir-gangwa-135735700.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://statetimes.in/former-hurriyat-chief-abdul-gani-bhat-passes-away/</t>
+          <t>https://bolchhattisgarh.in/divisional-level-nuakhai-milan-ceremony-of-dhurwa-samaj-in-jagdalpur-and-the-inauguration-program-of-newly-constructed-social-building-olerse/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cme-cum-brainstorming-session-organised-by-mru-gmc-jammu/</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
+          <t>https://eng.ruralvoice.in/cooperatives/kribhco-elects-v-sudhakar-chowdary-chairman-chandrapal-singh-yadav-vice-chairman.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://himachaldastak.com/chief-minister-tourism-start-up-scheme-gets-approval/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/himachal-government-will-bear-the-expenses-of-marriage-of-orphan-children-2216300</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/cm-will-inaugurate-the-buildings-of-animal-science-university-tomorrow-135971701.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://www.bhaskar.com/local/punjab/bathinda/news/on-the-birthday-of-shaheed-bhagat-singh-we-will-surround-the-chief-ministers-residence-hakam-singh-dhanetha-135947665.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-govt-makes-ekyc-mandatory-for-beneficiaries-of/cid17441579.htm</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
+          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/state/punjab/cashless-treatment-up-to-rs-10-lakh-punjab-first-state-in-the-country-to-launch-the-chief-minister-s-health-scheme-news-94860</t>
+          <t>https://vocaltv.in/rajasthan/amrita-haat-will-be-inaugurated-on-sundayphp/cid17448002.htm</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/rudrapur/story-uttarakhand-cm-pushkar-singh-dhami-visits-khatima-listens-to-public-concerns-201758294392599.html</t>
+          <t>https://vocaltv.in/bihar/safety-standards-checked-operation-of-patna-metrophp/cid17426826.htm</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
+          <t>https://www.newspuran.com/preparations-for-payment-of-more-than-rs-2-crore-to-acss-favorite-firm-ey</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.eurasiareview.com/19092025-modi-at-75-the-statesman-the-swayamsevak-and-the-question-of-succession-oped/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
+          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/2-more-doctors-appointed-in-dhaneta-hospital-2213561</t>
+          <t>https://navbharatlive.com/maharashtra/pune/congress-harshwardhan-sapkal-devendra-fadnavis-rss-constitution-statement-1362143.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/durg-bhilai/news/big-meetings-of-bjp-and-congress-on-the-same-day-in-durg-135965362.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ashoknagar/congress-mla-gopal-singh-chauhan-secretly-met-with-the-cm-mohan-yadav-in-ashok-nagar-sparking-speculation-about-his-entry-into-the-bjp-/articleshow/124019641.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/aligarh/story-aligarh-wholesalers-demand-action-against-fake-drug-dealers-at-cdf-up-annual-meeting-201758578893110.html</t>
+          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://raigarhtopnews.com/chief-minister-vishnudev-sai-attended-2/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-ministers-instructions-ready-on-dm-ground-zero-in-disaster-affected-areas/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
+          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/himachal-education-reform-cbse-curriculum-rajiv-gandhi-schools-student-loan-scheme-54-818476</t>
+          <t>https://ganadesh.com/salute-to-sadanand-singhs-legacy-cm-nitish-will-unveil-the-statue-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/setback-for-congress-karnataka-hc-invalidates-malur-mlas-election-orders-recounting-of-votes/articleshow/123923092.cms</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/nation/rajnath-shares-my-modi-story-praises-discipline-knowledge/56623</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://www.jagran.com/uttarakhand/haridwar-haridwar-news-saints-donate-34-lakh-to-cm-relief-fund-24055800.html</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/a-driver-was-bitten-by-a-snake-and-taken-to-the-hospital-but-was-released-as-soon-as-he-was-shown-to-a-doctor-in-ujjain/articleshow/123980598.cms</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/katni-who-is-katni-barwara-mla-dhirendra-singh-dhiru-gifted-gold-ring-cm-mohan-yadav-9643451.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
+          <t>https://www.prabhatkhabar.com/state/jharkhand/khunti/cm-and-chief-justice-in-khunti-today</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mahakal-mandir-pandit-pujari-appointments-controversy-indore-high-court-seeks-answers-ujjain-collector-in-3-months/articleshow/123947146.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/kaimur/news/bihar-has-taken-a-new-direction-under-the-leadership-of-chief-minister-nitish-135966397.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/ujjain-railway-station-accident-army-truck-caught-fire-loaded-in-goods-train-railway-staff-control-no-casualty-reported/articleshow/124024940.cms</t>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/hansi/news/hisar-hansi-market-encroachment-removal-drive-municipal-council-update-135951308.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://www.bhaskar.com/bihar-election/news/pappu-yadav-talks-to-pm-on-stage-both-laugh-out-loud-135932167.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/ujiyarpur-vidhan-sabha-chunav-analysis/</t>
+          <t>https://22scope.com/chief-minister-launched-the-web-portal-of-mukhyamantri-pratiya-yojana-under-bihar-bhavan-and-other-construction-workers-welfare-board/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-digvijay-singh-s-reply-to-siddharth-tiwari-s-statement-son-can-be-son-or-daughter-father-is-not-ang-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/RSS-leader-stresses-on-strengthening-Hindu-society-to-counter-global-conspiracies/2938144</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/education-minister-sunil-kumars-big-statement-on-tre-4-135982974.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
+          <t>https://www.bhaskar.com/local/himachal/mandi/news/himachal-news-mandi-maha-yagya-mp-kangana-ranaut-pm-modi-135940705.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.bhaskar.com/local/himachal/shimla/news/mandi-mp-kangana-ranaut-visit-disaster-affected-kullu-manikaran-pm-modi-birthday-himachal-135957922.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/news/harsh-chhikara-supports-uttar-kumar-rape-allegation-statement-135965440.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-harshita-soni-missing-case-update-harshita-found-delhi-135957260.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/inox-neo-energies-to-acquire-640-mw-hybrid-portfolio-from-evergreen-group-/78793</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
+          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/psp-projects-sets-world-record-with-umiya-dham-foundation/79013</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/congress-factionalism-came-out-in-the-open-in-front-of-the-leader-of-opposition/</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/wastewater-and-sewage-treatment/ramky-wins-rs-20.85-billion-godavari-water-project/79057</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.constructionworld.in/latest-construction-technology/tekla-user-days-2025-highlights-collaboration-and-tech-led-construction-/78852</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.gyanwani.com/33520/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/ntpc-plans-nuclear-power-projects-via-jv-and-standalone-routes/78900</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/highways-and-roads-infrastructure/govt-approves-rs-4.45-billion-mokama-munger-highway-project/78743</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/goa-approves-rs-1.92-billion-mapusa-bus-stand-projec/78876</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/gwalior-railway-station-redevelopment-set-for-swift-completion/78894</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
+          <t>https://www.deshsewak.org/hindi/news/218872</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-provided-financial-approval-of-rs-127-crore-for-various-development-schemes/</t>
+          <t>https://www.jagran.com/uttar-pradesh/ghaziabad-ncr-ghaziabad-news-robot-assisted-sewer-cleaning-pilot-project-launched-24053307.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://citiupdate.com/news/detailNews/104931</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
+          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
+          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
         </is>
       </c>
     </row>
@@ -2426,1505 +2426,1806 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
+          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
+          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/hisar/agriculture-university-hau-rabi-fair-cm-nayab-singh-saini-647591</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.babushahi.com/business.php?id=210834</t>
+          <t>https://devbhoomidarshan.in/cm-dhami-honored-the-artisans-and-weavers-of-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/uae-firms-keen-to-invest-in-indian-infra-banking-startups-logistics-sectors-commerce-minister-piyush-goyal/articleshow/124001887.cms</t>
+          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-today-19-september-program-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
+          <t>https://tejastoday.com/loans-provided-to-the-beneficiaries-of-chief-minister-youth-entrepreneur-scheme/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
+          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
+          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/cm-nayab-singh-saini-mega-road-upgradation-project-647580</t>
+          <t>https://www.kadwaghut.com/?p=260635</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
+          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.sabguru.com/haryana-cm-nayab-singh-saini-inaugurates-557-projects-worth-about-rs-117-crore-in-sonipat</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/transrail-expands-footprint-in-africa-with-new-epc-project/78806</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/smart-cities-projects/global-south-diplomats-visit-bhubaneswar-smart-city/78934</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/delhi-cm-rekha-gupta-launches-song-for-pm-narendra-modis-birthday/articleshow/123921234.cms</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/cerc-proposes-stricter-grid-deviation-rules-for-renewable-projects-/78995</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/coal-and-mining/government-to-promote-underground-coal-gasification-in-auctions/79070</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-ldb-2.0-to-boost-digital-logistics-tracking/79079</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/defence/indian-army-rolls-out-first-overhauled-arv-vt-72b-with-jcbl-group-partnership/79056</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-leads-2025-to-benchmark-state-logistics/79078</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/vikram-solar-secures-200-mw-order-to-expand-india---s-solar-capacity/78863</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://hindi.theprint.in/india/permanent-infrastructure-for-simhastha-will-be-built-only-with-consensus-farmers-will-be-protected-chief-minister-yadav/869129/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://www.abplive.com/states/himachal-pradesh/himachal-floods-rs-20000-crore-loss-cm-sukhvinder-singh-sukhu-statement-on-relief-efforts-ann-3013837</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
+          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
+          <t>https://www.dainikjagranmpcg.com/opinion/prime-minister-narendra-modi-is-the-champion-of-technology/article-33454</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/engineer-s-day-will-be-celebrated-with-the-resolution-of-public-welfare-survey-app-and-public-project-manage-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/rohtak/chief-minister-vishwakarma-samman-yojana-launched-artisans-will-get-a-top-up-incentive-of-rs-5000/</t>
+          <t>https://www.khaskhabar.com/local/haryana/hisar-news/news-public-money-will-be-used-for-the-public-good-nayab-singh-saini-news-hindi-1-754587-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/tamilnadu-chief-minister-stalin-launches-anbu-karangal-scheme-hindi-news-hin25091503706</t>
+          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
+          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-viksit-bharat-viksit-uttar-pradesh-2047-workshop-in-gorakhpur-24049561.html</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/foundation-stone-laid-for-8-link-road-projects-worth-rs-1215-crore-135988387.html</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
+          <t>https://krantiodishanews.in/post/13872</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
+          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
+          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://cnin.co.in/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%BE-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80-%E0%A4%AA%E0%A4%B0-%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%BF%E0%A4%95.../70476</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
+          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
+          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
+          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://rghnews.com/cg-news-raipur-62/</t>
+          <t>https://www.bhaskar.com/local/bihar/purnia/news/pm-will-inaugurate-airport-and-hold-public-meeting-in-3-hours-135923374.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://rghnews.com/cg-news-today-89/</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/news/modi-government-reduced-gst-rates-135928493.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
+          <t>https://www.bhaskar.com/career/news/pm-modi-launches-odisha-governments-subhadra-yojana-education-minister-atishi-marlena-will-be-the-new-chief-minister-of-delhi-133658792.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
+          <t>https://www.bhaskar.com/local/bihar/jehanabad/news/tejashwi-bihar-adhikar-yatra-start-from-jehanabad-135927540.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
+          <t>https://www.ruralvoice.in/agribusiness/mother-dairy-reduces-prices-to-pass-on-gst-benefits-to-consumers.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://smefutures.com/moil-starts-manganese-exports-as-state-trading-enterprise/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/maharashtra-urges-centre-to-double-onion-export-subsidy-to-support-farmers</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/amit-shah-advises-farmers-to-reduce-use-of-pesticides-and-fertilizers-swm-1281204-2025-09-22</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/uttar-pradesh/story/yogi-adityanath-writes-pm-narendra-modi-birthday-wishes-ntc-dskc-2335103-2025-09-17</t>
+          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/piyush-goyal-to-visit-uae-for-13th-india-uae-high-level-task-force-on-investments/78929</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
+          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://newsheight.com/big-breaking-chief-minister-pushkar-singh-dhami-impressed-by-the-overflows/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
+          <t>https://ibgnews.com/2025/09/20/shri-h-m-bangur-chairman-shree-cement-conferred-honorary-doctorate-by-kiit-university/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/sukma/news/awareness-was-also-created-about-women-empowerment-in-the-workshop-135978839.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/news/sonipat-updates-haryana-cm-saaini-seva-pakhwada-dcrsut-murahtal-program-135981755.html</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/india-us-ties-tested-after-trump-attack-yet-still-stronger-than-chinas-trust-gap-says-us-foreign-policy-expert/articleshow/123939627.cms</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://smefutures.com/india-oman-trade-agreement-fta-oman-trade-deal/</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/eu-eyes-deeper-india-partnership-despite-concerns-over-moscow-ties/articleshow/123943367.cms</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/indias-exports-likely-to-grow-6-per-cent-this-year-piyush-goyal/articleshow/123947681.cms</t>
+          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/igf-qetci-sign-pact-to-develop-uk-india-quantum-value-chain-map/articleshow/123996773.cms</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/us-revokes-sanctions-exemption-on-irans-chabahar-port-what-it-means-for-indias-strategic-gateway/articleshow/123979793.cms</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/india-in-advanced-talks-with-oman-for-fta-open-to-trade-deals-with-other-gcc-nations-piyush-goyal/articleshow/124001364.cms</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/tripura-opposition-unhappy-with-no-business-in-assembly-on-sept-22-due-to-pm-modis-visit/articleshow/123999325.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-pm-narendra-modi-purnia-rally-nitish-kumar-statement-on-lalan-singh-nda-politics-analysis-bihar-chunav-9628128.html</t>
+          <t>https://www.krishakjagat.org/news/cm-yadav-went-to-the-fields-and-inspected-the-affected-crops-said-farmers-should-not-worry-every-field-will-be-surveyed/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
+          <t>https://www.krishakjagat.org/national-news/todays-weather-very-heavy-rain-alert-in-northeast-and-maharashtra-monsoon-returns-to-rajasthan-punjab-gujarat/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
+          <t>https://www.financialexpress.com/policy/economy-india-us-agree-to-step-up-efforts-for-early-bta-3979894/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india--new-zealand-fta-talks-advance-in-queenstown/79087</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://www.facebook.com/BBCnewsHindi/posts/%E0%A4%9C%E0%A4%AF%E0%A4%B0%E0%A4%BE%E0%A4%AE-%E0%A4%B0%E0%A4%AE%E0%A5%87%E0%A4%B6-%E0%A4%AC%E0%A5%8B%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%95%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%87%E0%A4%95%E0%A4%BC%E0%A4%B2%E0%A5%8C%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A5%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%80-%E0%A4%96%E0%A4%BC%E0%A4%AC%E0%A4%B0-h/905180755408570/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/bihar-chief-minister-nitish-kumar-met-union-home-minister-amit-shah/</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-politics-birendra-singh-created-an-atmosphere-for-kumari-selja-bhupendra-hooda-turned-tables-said-neither-tired-nor-retired-24056405.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/newsletters/morning-dispatch/the-h-1b-silver-lining-festive-sales-day-1-surge/articleshow/124059068.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-giriraj-singh-ignited-another-fire-in-the-mahagathbandhan-saying-rahul-took-political-advantage-of-tejashwi/articleshow/123979673.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/chandigarh-asks-haryana-school-teachers-135958903.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/bizarre-climate-ideas-show-how-far-off-track-we-are/articleshow/123965955.cms</t>
+          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.etvbharat.com/hi/!state/marathon-in-kurukshetra-namo-youth-run-2025-cm-nayab-saini-on-parivarvad-haryana-news-hrs25092100814</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://ind24.tv/news/scindia_MP</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-nabha-farmers-protest-dispute-female-dsp-mandeep-news-135984706.html</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-bathinda-court-again-issues-summons-bjp-mp-actor-kangana-ranaut-news-135933597.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+          <t>https://hindi.oneindia.com/news/bhopal/farmers-agitation-against-land-pooling-act-demonstration-by-bharatiya-kisan-sangh-and-karni-sena-1386239.html</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/uttarakhand-events-were-held-across-the-state-on-prime-minister-modis-birthday-cm-dhami-inaugurated-the-swachh-utsav-2025-program</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
+          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+          <t>https://krishijagran.com/news/dr-jitendra-singh-calls-biotechnology-india-s-next-industrial-revolution-highlights-bio-e3-policy-and-ai-healthcare-initiative/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/niti-aayog-launches-ai-roadmap-and-frontier-tech-repository/78832</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/asm-tech-to-invest-rs-2.50-bn-in-tamil-nadu/78907</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/godrej-finance--muthoot-join-hands-to-boost-msme-lending/79061</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+          <t>https://www.bhaskar.com/local/punjab/amritsar/news/amritsar-durgiana-temple-langoor-mela-navratri-2025-135978487.html</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://statetimes.in/dc-jammu-reviews-functioning-of-swd/</t>
+          <t>https://dainikdehat.com/states/uttar-pradesh/problems-of-farmers-cows-and-h1b-visa-holders-persist-akhilesh-targets-bjp</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/business/news/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-297667</t>
+          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://cg24news.in/bjp-20925</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-utensils-bank-135983940.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-news-rao-narbir-singh-said-namo-van-will-be-established-at-75-places-in-haryana-during-seva-pakhwada/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/10-eminent-agricultural-scientists-urge-pm-modi-to-expedite-clearance-for-gm-mustard.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B5%C2%B3%C2%B7&amp;fontname=Mangal&amp;LocID=32&amp;pubdate=19%20Sep%202025</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-22-september-2025-3492207.html</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links_Shivraj Singh Chauhan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A543"/>
+  <dimension ref="A1:A490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,56 +452,56 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
@@ -515,1407 +515,1407 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>http://www.uniindia.com/photoes/638071.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>https://www.uniindia.com/photoes/638794.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111289</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/pm-modi-birthday-shivraj-singh-chouhan-launches-healthy-women-strong-family-campaign-plants-75-saplings-in-pus</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.technologyforyou.org/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/after-vijayvargiya-meeting-with-home-minister-amit-shah-bjp-held-high-level-meeting-at-cm-house-madhya-pradesh-news-mps25092003187</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://mediawala.in/governance-hemant-will-be-able-to-form-his-team-on-the-decided-formula/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-17-18-september-live-updates-pm-narendra-modi-75th-birthday-bihar-election-bjp-amit-shah-rahul-gandhi-supreme-court/4145200/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rahli-advocate-association-election-ramanand-patel-new-president/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://indianlooknews.com/?p=56810</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bjp-mla-rajeev-singh-parichha-and-mla-ravi-sharma-came-face-to-face-over-inspector-in-jhansi-uttar-pradesh-news-ups25091500787</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/sub-inspector-sunil-kumar-rai-slaps-bjp-worker-in-mirzapur-ssp-suspended-departmental-inquiry-started-uttar-pradesh-news-ups25092003608</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/articles/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/ghaziabad-farmer-neelam-tyagi-honoured-with-dr-norman-e-borlaug-innovative-farmer-award-2025.html</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://krishijagran.com/news/govt-signs-mous-with-4-states-nirdpr-to-boost-rural-livelihoods-digital-innovations-under-day-nrlm/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://ndtv.in/jammu-kashmir-news/jammu-flood-affected-farmers-these-announcements-to-provide-compensation-9311326</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bhartiya-mazdoor-sangh-demands-national-labour-day.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://www.aajsamaaj.com/58-state-of-the-art-libraries-to-open-soon-in-punjab-sond/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://www.jammulinksnews.com/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.thehansindia.com/telangana/brs-leader-condemns-inhumane-treatment-of-muslims-demanding-graveyard-1006465</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/food-grain-production-expected-to-increase-by-24-percent-despite-floods-and-disasters-1278860-2025-09-17</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
+          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/state/ap-govt-offers-rs-800-incentive-per-bag-to-farmers-who-cut-urea-use.html</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india-plans-rs-2-billion-fund-to-boost-infrastructure-finance/78815</t>
+          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cbi-chargesheets-anil-ambani-rana-kapoor-in-rs-2796-crore-corruption-case/</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/punjab-and-haryana/chandigarh/registration-for-cashless-treatment-rs-10-lakh-under-chief-minister-health-scheme-will-start-from-september-23-bhagwant-mann-announces/articleshow/124050803.cms</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
+          <t>https://22scope.com/bihar-women-said-thanks-thanks-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/career/news/union-cabinet-approves-bio-ride-scheme-atishi-will-take-oath-as-chief-minister-on-september-21-133669316.html</t>
+          <t>https://hindikhabar.com/haryana-storage-capacity-increase-central-government-approval/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
+          <t>https://www.jagran.com/haryana/null-haryana-government-orders-police-officers-to-meet-people-for-one-hour-each-morning-and-evening-to-resolve-complaints-24052783.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://argusenglish.in/national/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/lucknow/up-bjp-and-rss-meeting-before-panchayat-chunav-and-assembly-poll-3-leaders-gets-responsibility-news/articleshow/123899002.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/maharashtra-indian-railways-renames-ahmednagar-railway-station-as-ahilyanagar/</t>
+          <t>https://www.bhaskar.com/local/bihar/kishanganj/kochadhaman/news/jeevikas-annual-general-meeting-held-at-altahat-kochadhaman-135950707.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/darbhanga/news/darbhanga-cricket-associations-annual-general-meeting-was-held-new-district-committee-was-elected-135989912.html</t>
+          <t>https://www.abplive.com/states/haryana/haryana-cm-nayab-singh-saini-on-navratri-subsidy-to-farmers-paddy-procurement-adoption-of-swadeshi-3016726</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
+          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
+          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/reconstruction-of-disaster-affected-areas-is-top-priority/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
+          <t>https://www.amarujala.com/dehradun/new-gst-rates-will-be-implemented-in-from-today-cm-dhami-said-state-economy-will-be-strengthened-uttarakhand-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
+          <t>https://www.jagran.com/bihar/khagaria-nitish-kumars-khagaria-visit-statue-unveiling-and-development-projects-24051481.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/charkhi-dadri/news/charkhi-dadri-mla-sunil-satpal-sangwan-monsoon-session-assembly-dadri-rohtak-road-tender-construction-issue-public-works-department-minister-ranbir-gangwa-135735700.html</t>
+          <t>https://www.prabhatkhabar.com/state/bihar/khagaria/preparations-in-full-swing-in-pansalwa</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
+          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://bolchhattisgarh.in/divisional-level-nuakhai-milan-ceremony-of-dhurwa-samaj-in-jagdalpur-and-the-inauguration-program-of-newly-constructed-social-building-olerse/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
+          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
@@ -1929,147 +1929,147 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/cooperatives/kribhco-elects-v-sudhakar-chowdary-chairman-chandrapal-singh-yadav-vice-chairman.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
+          <t>https://www.amarujala.com/india-news/bihar-politics-will-the-combination-of-rahul-and-tejashwi-be-a-hit-how-strongly-will-nitish-kumar-fight-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/instructions-to-remove-ai-video-of-pms-mother-135941376.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
+          <t>https://www.bhaskar.com/local/haryana/jind/news/devendra-atri-vs-brijendra-singh-high-court-petition-uchana-vote-recounting-case-135957437.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
+          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
+          <t>https://www.kisantak.in/knowledge/story/know-all-about-chili-variety-kashi-anmol-which-gives-higher-yield-to-farmers-1278361-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/cm-will-inaugurate-the-buildings-of-animal-science-university-tomorrow-135971701.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/bathinda/news/on-the-birthday-of-shaheed-bhagat-singh-we-will-surround-the-chief-ministers-residence-hakam-singh-dhanetha-135947665.html</t>
+          <t>https://www.freepressjournal.in/bhopal/uttar-pradesh-man-who-walks-3600-km-to-promote-organic-food-fight-junk-diet-reaches-bhopal</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
+          <t>https://www.freepressjournal.in/bhopal/bhopal-animal-birth-control-centre-accused-of-keeping-dogs-captive-for-over-a-month</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/rajasthan/amrita-haat-will-be-inaugurated-on-sundayphp/cid17448002.htm</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/bihar/safety-standards-checked-operation-of-patna-metrophp/cid17426826.htm</t>
+          <t>https://hindi.oneindia.com/news/bhopal/demonstration-of-mp-guest-teachers-gathered-in-bhopal-ambedkar-park-demand-for-regularization-1386979.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.newspuran.com/preparations-for-payment-of-more-than-rs-2-crore-to-acss-favorite-firm-ey</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.eurasiareview.com/19092025-modi-at-75-the-statesman-the-swayamsevak-and-the-question-of-succession-oped/</t>
+          <t>https://www.freepressjournal.in/bhopal/watch-behno-chappal-taiyar-rakhna-mp-cm-mohan-yadav-advices-ladli-behna-slams-congress-over-liquor-remark-in-ashoknagar</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
+          <t>https://www.bhopalsamachar.com/2025/09/bhopal-rss.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/congress-harshwardhan-sapkal-devendra-fadnavis-rss-constitution-statement-1362143.html</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
+          <t>https://www.etvbharat.com/hi/!bharat/prime-minister-narendra-modi-at-75-years-time-line-of-major-events-in-modi-life-hindi-news-hin25091604966</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/durg-bhilai/news/big-meetings-of-bjp-and-congress-on-the-same-day-in-durg-135965362.html</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
@@ -2090,98 +2090,98 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
+          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://www.prabhatkhabar.com/state/bihar/khagaria/on-25th-the-c-m-will-address-a-meeting-in-pansalwa</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/gadchiroli-samruddha-panchayat-abhiyan-launch-1360071.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
+          <t>https://www.etvbharat.com/hi/!state/rewa-pandit-srinivas-tiwari-100th-birth-anniversary-statue-unveiling-congress-convention-madhya-pradesh-news-mps25091800671</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://ganadesh.com/salute-to-sadanand-singhs-legacy-cm-nitish-will-unveil-the-statue-on-september-25/</t>
+          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.gyanwani.com/33520/</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/haridwar-haridwar-news-saints-donate-34-lakh-to-cm-relief-fund-24055800.html</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/katni-who-is-katni-barwara-mla-dhirendra-singh-dhiru-gifted-gold-ring-cm-mohan-yadav-9643451.html</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/state/jharkhand/khunti/cm-and-chief-justice-in-khunti-today</t>
+          <t>https://khabarwani.com/tour-program-of-honorable-shri-digvijay-singh-ji-rajya-sabha-mp-and-former-chief-minister-madhya-pradesh/</t>
         </is>
       </c>
     </row>
@@ -2195,56 +2195,56 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
+          <t>https://www.bhaskar.com/local/bihar/katihar/news/dainik-bhaskar-bhagalpur-tuesday-september-16-2025-18-135930944.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/hansi/news/hisar-hansi-market-encroachment-removal-drive-municipal-council-update-135951308.html</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/bihar-election/news/pappu-yadav-talks-to-pm-on-stage-both-laugh-out-loud-135932167.html</t>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/the-mayor-sent-a-245-page-reply-to-the-department-135936659.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-the-web-portal-of-mukhyamantri-pratiya-yojana-under-bihar-bhavan-and-other-construction-workers-welfare-board/</t>
+          <t>https://janpakshaajkal.com/the-wife-of-senior-journalist-pankaj-panwar-passed-away-by-chief-minister-pushkar-singh-dhami-and-director-general-information-banshidhar-tiwari/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
+          <t>https://www.bhaskar.com/local/haryana/karnal/news/haryana-congress-controversy-biraendra-singh-kumari-selja-bhupinder-singh-hooda-135961908.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/hearing-on-sir-in-supreme-court-in-today-135923491.html</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/education-minister-sunil-kumars-big-statement-on-tre-4-135982974.html</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
@@ -2279,28 +2279,28 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/mlas-controversial-statement-on-lord-chitragupta-135953638.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/sonipat/news/harsh-chhikara-supports-uttar-kumar-rape-allegation-statement-135965440.html</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-harshita-soni-missing-case-update-harshita-found-delhi-135957260.html</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/inox-neo-energies-to-acquire-640-mw-hybrid-portfolio-from-evergreen-group-/78793</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
@@ -2314,1918 +2314,1547 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/psp-projects-sets-world-record-with-umiya-dham-foundation/79013</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/wastewater-and-sewage-treatment/ramky-wins-rs-20.85-billion-godavari-water-project/79057</t>
+          <t>https://www.amarujala.com/bihar/patna/bihar-goa-cm-and-several-other-leaders-attended-the-naman-bankipur-event-nitin-naveen-targeted-the-rjd-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/latest-construction-technology/tekla-user-days-2025-highlights-collaboration-and-tech-led-construction-/78852</t>
+          <t>https://www.deshsewak.org/hindi/news/218872</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/ntpc-plans-nuclear-power-projects-via-jv-and-standalone-routes/78900</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/gohana/news/sonipat-murthal-dcrust-cm-nayab-saini-visit-preparations-update-135958608.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/highways-and-roads-infrastructure/govt-approves-rs-4.45-billion-mokama-munger-highway-project/78743</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/goa-approves-rs-1.92-billion-mapusa-bus-stand-projec/78876</t>
+          <t>https://www.etvbharat.com/hi/!state/cm-nitish-kumar-to-inaugurate-development-projects-in-bihar-worth-crores-bihar-news-brs25092201132</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/gwalior-railway-station-redevelopment-set-for-swift-completion/78894</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B2%C2%B0%C3%8E%C2%B1%C2%B8%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/20/2025</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.deshsewak.org/hindi/news/218872</t>
+          <t>https://www.livehindustan.com/bihar/bhagalpur/story-bihar-cm-launches-development-projects-worth-15-crores-in-kishanganj-201758545934858.html</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/ghaziabad-ncr-ghaziabad-news-robot-assisted-sewer-cleaning-pilot-project-launched-24053307.html</t>
+          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
+          <t>https://www.munaadi.com/news-details/Chief-Minister-to-inaugurate-51-Mahatari-Sadans-on-September-23-state-level-event-to-be-held-in-village-Karelibari-of-Dhamtari-district-Dhamtari-to-get-development-works-worth-Rs-246-crore</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/news/cm-nitish-to-visit-west-champaran-on-september-23-135969700.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
+          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
+          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/hisar/agriculture-university-hau-rabi-fair-cm-nayab-singh-saini-647591</t>
+          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
+          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://devbhoomidarshan.in/cm-dhami-honored-the-artisans-and-weavers-of-uttarakhand/</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-today-19-september-program-in-hindi/</t>
+          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/loans-provided-to-the-beneficiaries-of-chief-minister-youth-entrepreneur-scheme/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
+          <t>https://www.arthparkash.com/initiative-to-strengthen-road-infrastructure-in-haryana</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260635</t>
+          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/transrail-expands-footprint-in-africa-with-new-epc-project/78806</t>
+          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/smart-cities-projects/global-south-diplomats-visit-bhubaneswar-smart-city/78934</t>
+          <t>https://krantiodishanews.in/post/13872</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/cerc-proposes-stricter-grid-deviation-rules-for-renewable-projects-/78995</t>
+          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/coal-and-mining/government-to-promote-underground-coal-gasification-in-auctions/79070</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-ldb-2.0-to-boost-digital-logistics-tracking/79079</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/defence/indian-army-rolls-out-first-overhauled-arv-vt-72b-with-jcbl-group-partnership/79056</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-leads-2025-to-benchmark-state-logistics/79078</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/vikram-solar-secures-200-mw-order-to-expand-india---s-solar-capacity/78863</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/permanent-infrastructure-for-simhastha-will-be-built-only-with-consensus-farmers-will-be-protected-chief-minister-yadav/869129/</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/himachal-pradesh/himachal-floods-rs-20000-crore-loss-cm-sukhvinder-singh-sukhu-statement-on-relief-efforts-ann-3013837</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
+          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.dainikjagranmpcg.com/opinion/prime-minister-narendra-modi-is-the-champion-of-technology/article-33454</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
+          <t>https://www.etvbharat.com/hi/!state/delhi-government-will-give-six-thousand-rupees-every-month-to-those-who-take-care-of-disabled-delhi-news-dls25091603962</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/engineer-s-day-will-be-celebrated-with-the-resolution-of-public-welfare-survey-app-and-public-project-manage-2025-09-15</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/hisar-news/news-public-money-will-be-used-for-the-public-good-nayab-singh-saini-news-hindi-1-754587-KKN.html</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/rohtak/vishwakarma-jayanti-haryana-chief-minister-vishwakarma-samman-yojana-benefits-647004</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
+          <t>https://www.ibc24.in/uttarakhand/cm-pushkar-singh-dhami-birthday-2025-wishes-from-amit-shah-yogi-no-celebration-announced-3254134.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/foundation-stone-laid-for-8-link-road-projects-worth-rs-1215-crore-135988387.html</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13872</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
+          <t>https://22scope.com/the-chief-minister-transferred-through-dbt-in-the-bank-account-of-students-under-various-welfare-schemes-of-the-education-department/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/</t>
+          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
+          <t>https://www.ptinews.com/story/national/karnataka-hc-infers-consent-of-biological-father-in-minors-adoption-case/2939691</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.ptinews.com/story/national/pm-arrives-in-tripura-to-inaugurate-redeveloped-tripureswari-temple/2937934</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/purnia/news/pm-will-inaugurate-airport-and-hold-public-meeting-in-3-hours-135923374.html</t>
+          <t>https://www.ptinews.com/story/national/70-arrested-with-illegal-arms-drugs-under-delhi-polices-operation-aaghat/2933128</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/bettiah/news/modi-government-reduced-gst-rates-135928493.html</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/career/news/pm-modi-launches-odisha-governments-subhadra-yojana-education-minister-atishi-marlena-will-be-the-new-chief-minister-of-delhi-133658792.html</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/jehanabad/news/tejashwi-bihar-adhikar-yatra-start-from-jehanabad-135927540.html</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/agribusiness/mother-dairy-reduces-prices-to-pass-on-gst-benefits-to-consumers.html</t>
+          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
+          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
+          <t>https://22scope.com/on-september-22-the-fight-for-the-rights-of-pacs-employees-intensified-on-22-september/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
+          <t>https://www.thehansindia.com/andhra-pradesh/womens-empowerment-conference-calls-for-action-beyond-slogans-1006774</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
+          <t>https://www.abplive.com/states/up-uk/noida-news-grand-launch-of-mission-shakti-phase-5-noida-resonated-with-the-message-of-women-empowerment-ann-3016602</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/pratapgarh-kunda/story-mission-shakti-phase-5-launched-for-women-s-empowerment-and-safety-in-pratapgarh-201758463458936.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
+          <t>https://vocaltv.in/rajasthan/launch-ceremony-of-healthy-womenphp/cid17431249.htm</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
+          <t>https://www.etvbharat.com/hi/!state/healthy-women-empowered-family-campaign-will-be-run-across-country-on-pms-birthday-jharkhand-news-jhs25091600888</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
+          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
+          <t>https://hindi.opindia.com/reports/mission-shakti-phase-5-begin-in-uttar-pradesh-during-navratri-cm-yogi-announces/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://www.etvbharat.com/hi/!state/rps-passing-out-pared-cm-attend-the-function-in-jaipur-rajasthan-news-rjs25091901773</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://vlesociety.com/bihar-mukhyamantri-mahila-rojgar-yojana-kist-update/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/piyush-goyal-to-visit-uae-for-13th-india-uae-high-level-task-force-on-investments/78929</t>
+          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://upkiran.org/Uttarakhand-BJP-new-team-announced-Woman-general-secretary-for-first-time-know-full-list</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
+          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-chief-minister-pushkar-singh-dhami-impressed-by-the-overflows/</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://ibgnews.com/2025/09/20/shri-h-m-bangur-chairman-shree-cement-conferred-honorary-doctorate-by-kiit-university/</t>
+          <t>https://www.kisantak.in/knowledge/story/pm-modi-at-75-how-pm-kisan-samman-nidhi-launched-by-pm-modi-becomes-the-biggest-support-for-farmers-1278751-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/sukma/news/awareness-was-also-created-about-women-empowerment-in-the-workshop-135978839.html</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://mradubhashi.com/news.php?id=india-can-achieve-8-growth-target-with-artificial-intelligence-niti-aayog-report-576577</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
+          <t>https://www.patrika.com/patrika-special/mp-politics-wave-rises-demand-to-make-this-leader-cm-intensifies-19948637</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-meeting-between-cm-dr-yadav-and-assembly-speaker-tomar-discussion-continued-in-a-closed-room-for-ha-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://www.jagran.com/bihar/patna-city-nitish-kumar-meets-amit-shah-rjd-calls-it-surrender-24052024.html</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
+          <t>https://www.statemirror.com/state/bihar/lalu-yadav-brainchild-bhura-baal-returns-in-bihar-election-2025-what-impact-on-cast-politics-151176</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/sonipat/news/sonipat-updates-haryana-cm-saaini-seva-pakhwada-dcrsut-murahtal-program-135981755.html</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/dynasty-politics-nepotism-has-deep-roots-in-congress-too-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
+          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://www.bbc.com/hindi/articles/cj6xr010dldo</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
+          <t>https://hindi.news18.com/news/haryana/chandigarh-city-rahul-gandhi-habit-of-making-false-allegations-then-running-away-haryana-cm-nayab-singh-saini-on-vote-chori-9647747.html</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://www.etvbharat.com/hi/!bharat/kosi-in-bihar-election-it-is-nitish-kumar-who-wins-not-lalu-yadav-story-of-three-yadavs-of-politics-hindi-news-brn25091602128</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1188206</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://www.etvbharat.com/hi/!state/former-chief-minister-ashok-gehlot-raised-questions-on-election-commission-rajasthan-news-rjs25092001128</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
+          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
+          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://khabarsameeksha.com/cm-dhami-reached-kesarwala-maldevata-on-inspection/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/cm-yadav-went-to-the-fields-and-inspected-the-affected-crops-said-farmers-should-not-worry-every-field-will-be-surveyed/</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/todays-weather-very-heavy-rain-alert-in-northeast-and-maharashtra-monsoon-returns-to-rajasthan-punjab-gujarat/</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-india-us-agree-to-step-up-efforts-for-early-bta-3979894/</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india--new-zealand-fta-talks-advance-in-queenstown/79087</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
+          <t>https://www.etvbharat.com/hi/!state/cm-mewat-upliftment-scheme-benefits-on-passing-competitive-exams-scholarship-in-nuh-haryana-news-hrs25091803715</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BBCnewsHindi/posts/%E0%A4%9C%E0%A4%AF%E0%A4%B0%E0%A4%BE%E0%A4%AE-%E0%A4%B0%E0%A4%AE%E0%A5%87%E0%A4%B6-%E0%A4%AC%E0%A5%8B%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%95%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%87%E0%A4%95%E0%A4%BC%E0%A4%B2%E0%A5%8C%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A5%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%80-%E0%A4%96%E0%A4%BC%E0%A4%AC%E0%A4%B0-h/905180755408570/</t>
+          <t>https://www.bhaskar.com/local/bihar/aurangabad/news/reduction-in-gst-rates-will-increase-purchasing-135936513.html</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://timesofindia.indiatimes.com/business/india-business/reduced-prices-of-farm-equipment-under-gst-2-0-will-help-air-pollution-abatement-efforts/articleshow/124001260.cms</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/panchkula-haryana-politics-birendra-singh-created-an-atmosphere-for-kumari-selja-bhupendra-hooda-turned-tables-said-neither-tired-nor-retired-24056405.html</t>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-giriraj-singh-ignited-another-fire-in-the-mahagathbandhan-saying-rahul-took-political-advantage-of-tejashwi/articleshow/123979673.cms</t>
+          <t>https://www.etvbharat.com/hi/!state/pm-narendra-modi-birthday-uttarakhand-bjp-swachhotsav-abhiyan-program-uttarakhand-news-uts25091701295</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/panchkula/news/chandigarh-asks-haryana-school-teachers-135958903.html</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/marathon-in-kurukshetra-namo-youth-run-2025-cm-nayab-saini-on-parivarvad-haryana-news-hrs25092100814</t>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
+          <t>https://suryasamachar.com/2025/09/18/cm-rekha-gupta-planted-sapling-in-mother-name-diplomats-from-70-countries-participated-one-tree-in-mother-name/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/forest-friends-will-be-appointed-to-overcome-the-shortage-of-staff-in-the-forest-2214886</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://ind24.tv/news/scindia_MP</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-cm-bhajanlal-sharma-planted-a-tree-at-the-chief-minister-residence-and-gave-the-message-of-environmental-protection-news-hindi-1-754747-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.khaskhabar.com/local/haryana/chandigarh-news/news-haryana-government-working-to-modernize-healthcare-facilities-in-the-state-nayab-singh-saini-news-hindi-1-754146-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://garimatimes.in/on-pm-modis-birthday-cm-saini-did-cleanliness-work-in-rohtak-planted-a-tree-and-flagged-off-namo-marathon/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://www.haryanaekhabar.com/gurugram/haryana-to-become-medical-hub-mbbs-seats-to-increase-from-700-to-2600-know-the-target-after-four-years/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
+          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-nabha-farmers-protest-dispute-female-dsp-mandeep-news-135984706.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/19/del27-jk-chouhan-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-bathinda-court-again-issues-summons-bjp-mp-actor-kangana-ranaut-news-135933597.html</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
+          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/farmers-agitation-against-land-pooling-act-demonstration-by-bharatiya-kisan-sangh-and-karni-sena-1386239.html</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/dr-jitendra-singh-calls-biotechnology-india-s-next-industrial-revolution-highlights-bio-e3-policy-and-ai-healthcare-initiative/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://makdaiexpress24.com/aaj-ka-rashifal-today-know-the-horoscope-of-september-16/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/niti-aayog-launches-ai-roadmap-and-frontier-tech-repository/78832</t>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/asm-tech-to-invest-rs-2.50-bn-in-tamil-nadu/78907</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/godrej-finance--muthoot-join-hands-to-boost-msme-lending/79061</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/amritsar/news/amritsar-durgiana-temple-langoor-mela-navratri-2025-135978487.html</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>https://dainikdehat.com/states/uttar-pradesh/problems-of-farmers-cows-and-h1b-visa-holders-persist-akhilesh-targets-bjp</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-utensils-bank-135983940.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-news-rao-narbir-singh-said-namo-van-will-be-established-at-75-places-in-haryana-during-seva-pakhwada/</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>https://eng.ruralvoice.in/latest-news/10-eminent-agricultural-scientists-urge-pm-modi-to-expedite-clearance-for-gm-mustard.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B5%C2%B3%C2%B7&amp;fontname=Mangal&amp;LocID=32&amp;pubdate=19%20Sep%202025</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-22-september-2025-3492207.html</t>
         </is>
       </c>
     </row>
